--- a/Config/Datas/jingyuan_codex.xlsx
+++ b/Config/Datas/jingyuan_codex.xlsx
@@ -1,17 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="jingyuan_codex_def" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="jingyuan_codex_level" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="jingyuan_tune_tier" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="tiao_jing_concentration_level" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="jingyuan_type_def" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="jingyuan_type_pool" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jingyuan_codex_def" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jingyuan_codex_level" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jingyuan_tune_tier" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tiao_jing_concentration_level" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jingyuan_type_def" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jingyuan_type_pool" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jingyuan_type_info" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jingyuan_premium_essence" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jingyuan_premium_effect" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jingyuan_essence_level_map" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jingyuan_type_pool_enum" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="named_npc_jingyuan_type" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1533,6 +1539,632 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>map_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>npc_level_min</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>npc_level_max</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>essence_level</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>映射主键</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NPC等级下限</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NPC等级上限</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>精华等级</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>npc_1_10</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>npc_11_20</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>11</v>
+      </c>
+      <c r="D7" t="n">
+        <v>20</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>npc_21_plus</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>21</v>
+      </c>
+      <c r="D8" t="n">
+        <v>999</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>entry_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pool_id</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>type_id</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>demo.EJingYuanType</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>入口 id</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>精型池</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>精型枚举</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>权重</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>orc</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>OrcCommon</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>orc</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>OrcElite</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SignAries</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SignTaurus</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SignGemini</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SignCancer</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SignLeo</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SignVirgo</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>9</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SignLibra</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>10</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SignScorpio</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>11</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SignSagittarius</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>12</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>SignCapricorn</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>13</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>SignAquarius</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>14</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>SignPisces</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>character_key</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>type_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>demo.EJingYuanType</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CharacterKey</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>固定精型枚举</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -3232,4 +3864,5295 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>type_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>display_name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>icon_path</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>race_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>match_tag</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>sort_order</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>demo.EJingYuanType</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>精型枚举</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>图标</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>对应种族</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>匹配标签</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>排序</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>OrcCommon</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>兽人精元</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>jingyuan/orccommon</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>orc</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>orccommon</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>OrcElite</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>兽人精英精元</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>jingyuan/orcelite</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>orc</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>orcelite</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SignAries</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>白羊座精元</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>jingyuan/signaries</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>signaries</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SignTaurus</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>金牛座精元</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>jingyuan/signtaurus</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>signtaurus</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SignGemini</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>双子座精元</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>jingyuan/signgemini</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>signgemini</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>SignCancer</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>巨蟹座精元</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>jingyuan/signcancer</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>signcancer</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SignLeo</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>狮子座精元</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>jingyuan/signleo</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>signleo</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>SignVirgo</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>处女座精元</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>jingyuan/signvirgo</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>signvirgo</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>SignLibra</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>天秤座精元</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>jingyuan/signlibra</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>signlibra</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SignScorpio</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>天蝎座精元</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>jingyuan/signscorpio</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>signscorpio</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SignSagittarius</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>射手座精元</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>jingyuan/signsagittarius</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>signsagittarius</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SignCapricorn</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>摩羯座精元</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>jingyuan/signcapricorn</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>signcapricorn</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SignAquarius</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>水瓶座精元</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>jingyuan/signaquarius</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>signaquarius</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SignPisces</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>双鱼座精元</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>jingyuan/signpisces</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>human</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>signpisces</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>essence_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>type_id</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>display_name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>base_shelf_life_days</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>extra_affix_pool_id</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>source_tag</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>demo.EJingYuanType</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>精华定义 id</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>精型枚举</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>基础保质期天数</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>额外词条池</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>来源标签</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>premium_orccommon</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>OrcCommon</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>优质兽人精元</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>affix_orccommon</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>extract_or_event</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>premium_orcelite</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>OrcElite</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>优质兽人精英精元</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>affix_orcelite</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>extract_or_event</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>premium_signaries</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SignAries</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>优质白羊座精元</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>affix_signaries</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>extract_or_event</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>premium_signtaurus</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SignTaurus</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>优质金牛座精元</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>affix_signtaurus</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>extract_or_event</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>premium_signgemini</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SignGemini</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>优质双子座精元</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>affix_signgemini</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>extract_or_event</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>premium_signcancer</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>SignCancer</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>优质巨蟹座精元</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>affix_signcancer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>extract_or_event</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>premium_signleo</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SignLeo</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>优质狮子座精元</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>affix_signleo</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>extract_or_event</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>premium_signvirgo</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SignVirgo</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>优质处女座精元</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>affix_signvirgo</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>extract_or_event</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>premium_signlibra</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SignLibra</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>优质天秤座精元</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>affix_signlibra</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>extract_or_event</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>premium_signscorpio</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SignScorpio</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>优质天蝎座精元</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>affix_signscorpio</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>extract_or_event</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>premium_signsagittarius</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SignSagittarius</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>优质射手座精元</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>affix_signsagittarius</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>extract_or_event</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>premium_signcapricorn</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SignCapricorn</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>优质摩羯座精元</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>affix_signcapricorn</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>extract_or_event</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>premium_signaquarius</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SignAquarius</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>优质水瓶座精元</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>affix_signaquarius</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>extract_or_event</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>premium_signpisces</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SignPisces</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>优质双鱼座精元</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>affix_signpisces</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>extract_or_event</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F215"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>type_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>drop_level</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>concentration_floor</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>attr_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>attr_value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>demo.EJingYuanType</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>精型枚举</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>掉落等级</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>浓度下限(0-100)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>EYCAttribute</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>属性加成</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>OrcCommon</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>OrcCommon</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>25</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>OrcCommon</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>50</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>OrcCommon</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>75</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>OrcCommon</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>100</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>OrcCommon</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>OrcCommon</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>25</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>OrcCommon</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>50</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>OrcCommon</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>75</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>OrcCommon</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>100</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>OrcCommon</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>OrcCommon</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>25</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>OrcCommon</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>50</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>OrcCommon</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="n">
+        <v>75</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>OrcCommon</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>100</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>OrcElite</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>OrcElite</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>25</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>OrcElite</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>50</v>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>OrcElite</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>75</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>OrcElite</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>100</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>OrcElite</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>OrcElite</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>25</v>
+      </c>
+      <c r="E27" t="n">
+        <v>3</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>OrcElite</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>50</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>OrcElite</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="n">
+        <v>75</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>OrcElite</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>100</v>
+      </c>
+      <c r="E30" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>OrcElite</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>OrcElite</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>25</v>
+      </c>
+      <c r="E32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>OrcElite</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" t="n">
+        <v>50</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>OrcElite</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" t="n">
+        <v>75</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>OrcElite</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" t="n">
+        <v>100</v>
+      </c>
+      <c r="E35" t="n">
+        <v>3</v>
+      </c>
+      <c r="F35" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SignAries</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="n">
+        <v>3</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SignAries</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>25</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3</v>
+      </c>
+      <c r="F37" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SignAries</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>50</v>
+      </c>
+      <c r="E38" t="n">
+        <v>3</v>
+      </c>
+      <c r="F38" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SignAries</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>75</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SignAries</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>100</v>
+      </c>
+      <c r="E40" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SignAries</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>SignAries</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" t="n">
+        <v>25</v>
+      </c>
+      <c r="E42" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>SignAries</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" t="n">
+        <v>50</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>SignAries</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" t="n">
+        <v>75</v>
+      </c>
+      <c r="E44" t="n">
+        <v>3</v>
+      </c>
+      <c r="F44" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SignAries</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" t="n">
+        <v>100</v>
+      </c>
+      <c r="E45" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SignAries</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>3</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="n">
+        <v>3</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SignAries</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" t="n">
+        <v>25</v>
+      </c>
+      <c r="E47" t="n">
+        <v>3</v>
+      </c>
+      <c r="F47" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SignAries</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>3</v>
+      </c>
+      <c r="D48" t="n">
+        <v>50</v>
+      </c>
+      <c r="E48" t="n">
+        <v>3</v>
+      </c>
+      <c r="F48" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>SignAries</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D49" t="n">
+        <v>75</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3</v>
+      </c>
+      <c r="F49" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>SignAries</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>3</v>
+      </c>
+      <c r="D50" t="n">
+        <v>100</v>
+      </c>
+      <c r="E50" t="n">
+        <v>3</v>
+      </c>
+      <c r="F50" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>SignTaurus</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>3</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>SignTaurus</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="n">
+        <v>25</v>
+      </c>
+      <c r="E52" t="n">
+        <v>3</v>
+      </c>
+      <c r="F52" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>SignTaurus</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="n">
+        <v>50</v>
+      </c>
+      <c r="E53" t="n">
+        <v>3</v>
+      </c>
+      <c r="F53" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>SignTaurus</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="n">
+        <v>75</v>
+      </c>
+      <c r="E54" t="n">
+        <v>3</v>
+      </c>
+      <c r="F54" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>SignTaurus</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="n">
+        <v>100</v>
+      </c>
+      <c r="E55" t="n">
+        <v>3</v>
+      </c>
+      <c r="F55" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>SignTaurus</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>3</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>SignTaurus</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" t="n">
+        <v>25</v>
+      </c>
+      <c r="E57" t="n">
+        <v>3</v>
+      </c>
+      <c r="F57" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>SignTaurus</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" t="n">
+        <v>50</v>
+      </c>
+      <c r="E58" t="n">
+        <v>3</v>
+      </c>
+      <c r="F58" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>SignTaurus</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" t="n">
+        <v>75</v>
+      </c>
+      <c r="E59" t="n">
+        <v>3</v>
+      </c>
+      <c r="F59" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>SignTaurus</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" t="n">
+        <v>100</v>
+      </c>
+      <c r="E60" t="n">
+        <v>3</v>
+      </c>
+      <c r="F60" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>SignTaurus</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>3</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="n">
+        <v>3</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>SignTaurus</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>3</v>
+      </c>
+      <c r="D62" t="n">
+        <v>25</v>
+      </c>
+      <c r="E62" t="n">
+        <v>3</v>
+      </c>
+      <c r="F62" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SignTaurus</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>3</v>
+      </c>
+      <c r="D63" t="n">
+        <v>50</v>
+      </c>
+      <c r="E63" t="n">
+        <v>3</v>
+      </c>
+      <c r="F63" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SignTaurus</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>3</v>
+      </c>
+      <c r="D64" t="n">
+        <v>75</v>
+      </c>
+      <c r="E64" t="n">
+        <v>3</v>
+      </c>
+      <c r="F64" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>SignTaurus</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>3</v>
+      </c>
+      <c r="D65" t="n">
+        <v>100</v>
+      </c>
+      <c r="E65" t="n">
+        <v>3</v>
+      </c>
+      <c r="F65" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>SignGemini</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
+        <v>3</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>SignGemini</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="n">
+        <v>25</v>
+      </c>
+      <c r="E67" t="n">
+        <v>3</v>
+      </c>
+      <c r="F67" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>SignGemini</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" t="n">
+        <v>50</v>
+      </c>
+      <c r="E68" t="n">
+        <v>3</v>
+      </c>
+      <c r="F68" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>SignGemini</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" t="n">
+        <v>75</v>
+      </c>
+      <c r="E69" t="n">
+        <v>3</v>
+      </c>
+      <c r="F69" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>SignGemini</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="n">
+        <v>100</v>
+      </c>
+      <c r="E70" t="n">
+        <v>3</v>
+      </c>
+      <c r="F70" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>SignGemini</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>2</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>3</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>SignGemini</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>2</v>
+      </c>
+      <c r="D72" t="n">
+        <v>25</v>
+      </c>
+      <c r="E72" t="n">
+        <v>3</v>
+      </c>
+      <c r="F72" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>SignGemini</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>2</v>
+      </c>
+      <c r="D73" t="n">
+        <v>50</v>
+      </c>
+      <c r="E73" t="n">
+        <v>3</v>
+      </c>
+      <c r="F73" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>SignGemini</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>2</v>
+      </c>
+      <c r="D74" t="n">
+        <v>75</v>
+      </c>
+      <c r="E74" t="n">
+        <v>3</v>
+      </c>
+      <c r="F74" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>SignGemini</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2</v>
+      </c>
+      <c r="D75" t="n">
+        <v>100</v>
+      </c>
+      <c r="E75" t="n">
+        <v>3</v>
+      </c>
+      <c r="F75" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SignGemini</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>3</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>3</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SignGemini</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>3</v>
+      </c>
+      <c r="D77" t="n">
+        <v>25</v>
+      </c>
+      <c r="E77" t="n">
+        <v>3</v>
+      </c>
+      <c r="F77" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>SignGemini</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>3</v>
+      </c>
+      <c r="D78" t="n">
+        <v>50</v>
+      </c>
+      <c r="E78" t="n">
+        <v>3</v>
+      </c>
+      <c r="F78" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>SignGemini</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>3</v>
+      </c>
+      <c r="D79" t="n">
+        <v>75</v>
+      </c>
+      <c r="E79" t="n">
+        <v>3</v>
+      </c>
+      <c r="F79" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>SignGemini</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>3</v>
+      </c>
+      <c r="D80" t="n">
+        <v>100</v>
+      </c>
+      <c r="E80" t="n">
+        <v>3</v>
+      </c>
+      <c r="F80" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>SignCancer</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="n">
+        <v>3</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>SignCancer</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="n">
+        <v>25</v>
+      </c>
+      <c r="E82" t="n">
+        <v>3</v>
+      </c>
+      <c r="F82" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>SignCancer</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="n">
+        <v>50</v>
+      </c>
+      <c r="E83" t="n">
+        <v>3</v>
+      </c>
+      <c r="F83" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>SignCancer</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" t="n">
+        <v>75</v>
+      </c>
+      <c r="E84" t="n">
+        <v>3</v>
+      </c>
+      <c r="F84" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SignCancer</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="n">
+        <v>100</v>
+      </c>
+      <c r="E85" t="n">
+        <v>3</v>
+      </c>
+      <c r="F85" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>SignCancer</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>2</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="n">
+        <v>3</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>SignCancer</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>2</v>
+      </c>
+      <c r="D87" t="n">
+        <v>25</v>
+      </c>
+      <c r="E87" t="n">
+        <v>3</v>
+      </c>
+      <c r="F87" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>SignCancer</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>2</v>
+      </c>
+      <c r="D88" t="n">
+        <v>50</v>
+      </c>
+      <c r="E88" t="n">
+        <v>3</v>
+      </c>
+      <c r="F88" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>SignCancer</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>2</v>
+      </c>
+      <c r="D89" t="n">
+        <v>75</v>
+      </c>
+      <c r="E89" t="n">
+        <v>3</v>
+      </c>
+      <c r="F89" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>SignCancer</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>2</v>
+      </c>
+      <c r="D90" t="n">
+        <v>100</v>
+      </c>
+      <c r="E90" t="n">
+        <v>3</v>
+      </c>
+      <c r="F90" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>SignCancer</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>3</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="n">
+        <v>3</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>SignCancer</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>3</v>
+      </c>
+      <c r="D92" t="n">
+        <v>25</v>
+      </c>
+      <c r="E92" t="n">
+        <v>3</v>
+      </c>
+      <c r="F92" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>SignCancer</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>3</v>
+      </c>
+      <c r="D93" t="n">
+        <v>50</v>
+      </c>
+      <c r="E93" t="n">
+        <v>3</v>
+      </c>
+      <c r="F93" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>SignCancer</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>3</v>
+      </c>
+      <c r="D94" t="n">
+        <v>75</v>
+      </c>
+      <c r="E94" t="n">
+        <v>3</v>
+      </c>
+      <c r="F94" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>SignCancer</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>3</v>
+      </c>
+      <c r="D95" t="n">
+        <v>100</v>
+      </c>
+      <c r="E95" t="n">
+        <v>3</v>
+      </c>
+      <c r="F95" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>SignLeo</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>1</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>3</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>SignLeo</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" t="n">
+        <v>25</v>
+      </c>
+      <c r="E97" t="n">
+        <v>3</v>
+      </c>
+      <c r="F97" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>SignLeo</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" t="n">
+        <v>50</v>
+      </c>
+      <c r="E98" t="n">
+        <v>3</v>
+      </c>
+      <c r="F98" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>SignLeo</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" t="n">
+        <v>75</v>
+      </c>
+      <c r="E99" t="n">
+        <v>3</v>
+      </c>
+      <c r="F99" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>SignLeo</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" t="n">
+        <v>100</v>
+      </c>
+      <c r="E100" t="n">
+        <v>3</v>
+      </c>
+      <c r="F100" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>SignLeo</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>2</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="n">
+        <v>3</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>SignLeo</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>2</v>
+      </c>
+      <c r="D102" t="n">
+        <v>25</v>
+      </c>
+      <c r="E102" t="n">
+        <v>3</v>
+      </c>
+      <c r="F102" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>SignLeo</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>2</v>
+      </c>
+      <c r="D103" t="n">
+        <v>50</v>
+      </c>
+      <c r="E103" t="n">
+        <v>3</v>
+      </c>
+      <c r="F103" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>SignLeo</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>2</v>
+      </c>
+      <c r="D104" t="n">
+        <v>75</v>
+      </c>
+      <c r="E104" t="n">
+        <v>3</v>
+      </c>
+      <c r="F104" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>SignLeo</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>2</v>
+      </c>
+      <c r="D105" t="n">
+        <v>100</v>
+      </c>
+      <c r="E105" t="n">
+        <v>3</v>
+      </c>
+      <c r="F105" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>SignLeo</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>3</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" t="n">
+        <v>3</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>SignLeo</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>3</v>
+      </c>
+      <c r="D107" t="n">
+        <v>25</v>
+      </c>
+      <c r="E107" t="n">
+        <v>3</v>
+      </c>
+      <c r="F107" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>SignLeo</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>3</v>
+      </c>
+      <c r="D108" t="n">
+        <v>50</v>
+      </c>
+      <c r="E108" t="n">
+        <v>3</v>
+      </c>
+      <c r="F108" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>SignLeo</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>3</v>
+      </c>
+      <c r="D109" t="n">
+        <v>75</v>
+      </c>
+      <c r="E109" t="n">
+        <v>3</v>
+      </c>
+      <c r="F109" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>SignLeo</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>3</v>
+      </c>
+      <c r="D110" t="n">
+        <v>100</v>
+      </c>
+      <c r="E110" t="n">
+        <v>3</v>
+      </c>
+      <c r="F110" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>SignVirgo</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>1</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" t="n">
+        <v>3</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>SignVirgo</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>1</v>
+      </c>
+      <c r="D112" t="n">
+        <v>25</v>
+      </c>
+      <c r="E112" t="n">
+        <v>3</v>
+      </c>
+      <c r="F112" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>SignVirgo</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>1</v>
+      </c>
+      <c r="D113" t="n">
+        <v>50</v>
+      </c>
+      <c r="E113" t="n">
+        <v>3</v>
+      </c>
+      <c r="F113" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>SignVirgo</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>1</v>
+      </c>
+      <c r="D114" t="n">
+        <v>75</v>
+      </c>
+      <c r="E114" t="n">
+        <v>3</v>
+      </c>
+      <c r="F114" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>SignVirgo</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>1</v>
+      </c>
+      <c r="D115" t="n">
+        <v>100</v>
+      </c>
+      <c r="E115" t="n">
+        <v>3</v>
+      </c>
+      <c r="F115" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>SignVirgo</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>2</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" t="n">
+        <v>3</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>SignVirgo</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>2</v>
+      </c>
+      <c r="D117" t="n">
+        <v>25</v>
+      </c>
+      <c r="E117" t="n">
+        <v>3</v>
+      </c>
+      <c r="F117" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>SignVirgo</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>2</v>
+      </c>
+      <c r="D118" t="n">
+        <v>50</v>
+      </c>
+      <c r="E118" t="n">
+        <v>3</v>
+      </c>
+      <c r="F118" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>SignVirgo</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>2</v>
+      </c>
+      <c r="D119" t="n">
+        <v>75</v>
+      </c>
+      <c r="E119" t="n">
+        <v>3</v>
+      </c>
+      <c r="F119" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>SignVirgo</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>2</v>
+      </c>
+      <c r="D120" t="n">
+        <v>100</v>
+      </c>
+      <c r="E120" t="n">
+        <v>3</v>
+      </c>
+      <c r="F120" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>SignVirgo</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>3</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" t="n">
+        <v>3</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>SignVirgo</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>3</v>
+      </c>
+      <c r="D122" t="n">
+        <v>25</v>
+      </c>
+      <c r="E122" t="n">
+        <v>3</v>
+      </c>
+      <c r="F122" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>SignVirgo</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>3</v>
+      </c>
+      <c r="D123" t="n">
+        <v>50</v>
+      </c>
+      <c r="E123" t="n">
+        <v>3</v>
+      </c>
+      <c r="F123" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>SignVirgo</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>3</v>
+      </c>
+      <c r="D124" t="n">
+        <v>75</v>
+      </c>
+      <c r="E124" t="n">
+        <v>3</v>
+      </c>
+      <c r="F124" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>SignVirgo</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>3</v>
+      </c>
+      <c r="D125" t="n">
+        <v>100</v>
+      </c>
+      <c r="E125" t="n">
+        <v>3</v>
+      </c>
+      <c r="F125" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>SignLibra</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>1</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" t="n">
+        <v>3</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>SignLibra</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>1</v>
+      </c>
+      <c r="D127" t="n">
+        <v>25</v>
+      </c>
+      <c r="E127" t="n">
+        <v>3</v>
+      </c>
+      <c r="F127" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>SignLibra</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>1</v>
+      </c>
+      <c r="D128" t="n">
+        <v>50</v>
+      </c>
+      <c r="E128" t="n">
+        <v>3</v>
+      </c>
+      <c r="F128" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>SignLibra</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>1</v>
+      </c>
+      <c r="D129" t="n">
+        <v>75</v>
+      </c>
+      <c r="E129" t="n">
+        <v>3</v>
+      </c>
+      <c r="F129" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>SignLibra</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>1</v>
+      </c>
+      <c r="D130" t="n">
+        <v>100</v>
+      </c>
+      <c r="E130" t="n">
+        <v>3</v>
+      </c>
+      <c r="F130" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>SignLibra</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>2</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" t="n">
+        <v>3</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>SignLibra</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>2</v>
+      </c>
+      <c r="D132" t="n">
+        <v>25</v>
+      </c>
+      <c r="E132" t="n">
+        <v>3</v>
+      </c>
+      <c r="F132" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>SignLibra</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>2</v>
+      </c>
+      <c r="D133" t="n">
+        <v>50</v>
+      </c>
+      <c r="E133" t="n">
+        <v>3</v>
+      </c>
+      <c r="F133" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>SignLibra</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>2</v>
+      </c>
+      <c r="D134" t="n">
+        <v>75</v>
+      </c>
+      <c r="E134" t="n">
+        <v>3</v>
+      </c>
+      <c r="F134" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>SignLibra</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>2</v>
+      </c>
+      <c r="D135" t="n">
+        <v>100</v>
+      </c>
+      <c r="E135" t="n">
+        <v>3</v>
+      </c>
+      <c r="F135" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>SignLibra</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>3</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" t="n">
+        <v>3</v>
+      </c>
+      <c r="F136" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>SignLibra</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>3</v>
+      </c>
+      <c r="D137" t="n">
+        <v>25</v>
+      </c>
+      <c r="E137" t="n">
+        <v>3</v>
+      </c>
+      <c r="F137" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>SignLibra</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>3</v>
+      </c>
+      <c r="D138" t="n">
+        <v>50</v>
+      </c>
+      <c r="E138" t="n">
+        <v>3</v>
+      </c>
+      <c r="F138" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>SignLibra</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>3</v>
+      </c>
+      <c r="D139" t="n">
+        <v>75</v>
+      </c>
+      <c r="E139" t="n">
+        <v>3</v>
+      </c>
+      <c r="F139" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>SignLibra</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>3</v>
+      </c>
+      <c r="D140" t="n">
+        <v>100</v>
+      </c>
+      <c r="E140" t="n">
+        <v>3</v>
+      </c>
+      <c r="F140" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>SignScorpio</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>1</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" t="n">
+        <v>3</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>SignScorpio</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>1</v>
+      </c>
+      <c r="D142" t="n">
+        <v>25</v>
+      </c>
+      <c r="E142" t="n">
+        <v>3</v>
+      </c>
+      <c r="F142" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>SignScorpio</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>1</v>
+      </c>
+      <c r="D143" t="n">
+        <v>50</v>
+      </c>
+      <c r="E143" t="n">
+        <v>3</v>
+      </c>
+      <c r="F143" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>SignScorpio</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>1</v>
+      </c>
+      <c r="D144" t="n">
+        <v>75</v>
+      </c>
+      <c r="E144" t="n">
+        <v>3</v>
+      </c>
+      <c r="F144" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>SignScorpio</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>1</v>
+      </c>
+      <c r="D145" t="n">
+        <v>100</v>
+      </c>
+      <c r="E145" t="n">
+        <v>3</v>
+      </c>
+      <c r="F145" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>SignScorpio</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>2</v>
+      </c>
+      <c r="D146" t="n">
+        <v>0</v>
+      </c>
+      <c r="E146" t="n">
+        <v>3</v>
+      </c>
+      <c r="F146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>SignScorpio</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>2</v>
+      </c>
+      <c r="D147" t="n">
+        <v>25</v>
+      </c>
+      <c r="E147" t="n">
+        <v>3</v>
+      </c>
+      <c r="F147" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>SignScorpio</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>2</v>
+      </c>
+      <c r="D148" t="n">
+        <v>50</v>
+      </c>
+      <c r="E148" t="n">
+        <v>3</v>
+      </c>
+      <c r="F148" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>SignScorpio</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>2</v>
+      </c>
+      <c r="D149" t="n">
+        <v>75</v>
+      </c>
+      <c r="E149" t="n">
+        <v>3</v>
+      </c>
+      <c r="F149" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>SignScorpio</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>2</v>
+      </c>
+      <c r="D150" t="n">
+        <v>100</v>
+      </c>
+      <c r="E150" t="n">
+        <v>3</v>
+      </c>
+      <c r="F150" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>SignScorpio</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>3</v>
+      </c>
+      <c r="D151" t="n">
+        <v>0</v>
+      </c>
+      <c r="E151" t="n">
+        <v>3</v>
+      </c>
+      <c r="F151" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>SignScorpio</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>3</v>
+      </c>
+      <c r="D152" t="n">
+        <v>25</v>
+      </c>
+      <c r="E152" t="n">
+        <v>3</v>
+      </c>
+      <c r="F152" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>SignScorpio</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>3</v>
+      </c>
+      <c r="D153" t="n">
+        <v>50</v>
+      </c>
+      <c r="E153" t="n">
+        <v>3</v>
+      </c>
+      <c r="F153" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>SignScorpio</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>3</v>
+      </c>
+      <c r="D154" t="n">
+        <v>75</v>
+      </c>
+      <c r="E154" t="n">
+        <v>3</v>
+      </c>
+      <c r="F154" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>SignScorpio</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>3</v>
+      </c>
+      <c r="D155" t="n">
+        <v>100</v>
+      </c>
+      <c r="E155" t="n">
+        <v>3</v>
+      </c>
+      <c r="F155" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>SignSagittarius</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>1</v>
+      </c>
+      <c r="D156" t="n">
+        <v>0</v>
+      </c>
+      <c r="E156" t="n">
+        <v>3</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>SignSagittarius</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>1</v>
+      </c>
+      <c r="D157" t="n">
+        <v>25</v>
+      </c>
+      <c r="E157" t="n">
+        <v>3</v>
+      </c>
+      <c r="F157" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>SignSagittarius</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>1</v>
+      </c>
+      <c r="D158" t="n">
+        <v>50</v>
+      </c>
+      <c r="E158" t="n">
+        <v>3</v>
+      </c>
+      <c r="F158" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>SignSagittarius</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>1</v>
+      </c>
+      <c r="D159" t="n">
+        <v>75</v>
+      </c>
+      <c r="E159" t="n">
+        <v>3</v>
+      </c>
+      <c r="F159" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>SignSagittarius</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>1</v>
+      </c>
+      <c r="D160" t="n">
+        <v>100</v>
+      </c>
+      <c r="E160" t="n">
+        <v>3</v>
+      </c>
+      <c r="F160" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>SignSagittarius</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>2</v>
+      </c>
+      <c r="D161" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" t="n">
+        <v>3</v>
+      </c>
+      <c r="F161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>SignSagittarius</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>2</v>
+      </c>
+      <c r="D162" t="n">
+        <v>25</v>
+      </c>
+      <c r="E162" t="n">
+        <v>3</v>
+      </c>
+      <c r="F162" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>SignSagittarius</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>2</v>
+      </c>
+      <c r="D163" t="n">
+        <v>50</v>
+      </c>
+      <c r="E163" t="n">
+        <v>3</v>
+      </c>
+      <c r="F163" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>SignSagittarius</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>2</v>
+      </c>
+      <c r="D164" t="n">
+        <v>75</v>
+      </c>
+      <c r="E164" t="n">
+        <v>3</v>
+      </c>
+      <c r="F164" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>SignSagittarius</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>2</v>
+      </c>
+      <c r="D165" t="n">
+        <v>100</v>
+      </c>
+      <c r="E165" t="n">
+        <v>3</v>
+      </c>
+      <c r="F165" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>SignSagittarius</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>3</v>
+      </c>
+      <c r="D166" t="n">
+        <v>0</v>
+      </c>
+      <c r="E166" t="n">
+        <v>3</v>
+      </c>
+      <c r="F166" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>SignSagittarius</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>3</v>
+      </c>
+      <c r="D167" t="n">
+        <v>25</v>
+      </c>
+      <c r="E167" t="n">
+        <v>3</v>
+      </c>
+      <c r="F167" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>SignSagittarius</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>3</v>
+      </c>
+      <c r="D168" t="n">
+        <v>50</v>
+      </c>
+      <c r="E168" t="n">
+        <v>3</v>
+      </c>
+      <c r="F168" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>SignSagittarius</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>3</v>
+      </c>
+      <c r="D169" t="n">
+        <v>75</v>
+      </c>
+      <c r="E169" t="n">
+        <v>3</v>
+      </c>
+      <c r="F169" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>SignSagittarius</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>3</v>
+      </c>
+      <c r="D170" t="n">
+        <v>100</v>
+      </c>
+      <c r="E170" t="n">
+        <v>3</v>
+      </c>
+      <c r="F170" t="n">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>SignCapricorn</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>1</v>
+      </c>
+      <c r="D171" t="n">
+        <v>0</v>
+      </c>
+      <c r="E171" t="n">
+        <v>3</v>
+      </c>
+      <c r="F171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>SignCapricorn</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>1</v>
+      </c>
+      <c r="D172" t="n">
+        <v>25</v>
+      </c>
+      <c r="E172" t="n">
+        <v>3</v>
+      </c>
+      <c r="F172" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>SignCapricorn</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>1</v>
+      </c>
+      <c r="D173" t="n">
+        <v>50</v>
+      </c>
+      <c r="E173" t="n">
+        <v>3</v>
+      </c>
+      <c r="F173" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>SignCapricorn</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>1</v>
+      </c>
+      <c r="D174" t="n">
+        <v>75</v>
+      </c>
+      <c r="E174" t="n">
+        <v>3</v>
+      </c>
+      <c r="F174" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>SignCapricorn</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>1</v>
+      </c>
+      <c r="D175" t="n">
+        <v>100</v>
+      </c>
+      <c r="E175" t="n">
+        <v>3</v>
+      </c>
+      <c r="F175" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>SignCapricorn</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>2</v>
+      </c>
+      <c r="D176" t="n">
+        <v>0</v>
+      </c>
+      <c r="E176" t="n">
+        <v>3</v>
+      </c>
+      <c r="F176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>SignCapricorn</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>2</v>
+      </c>
+      <c r="D177" t="n">
+        <v>25</v>
+      </c>
+      <c r="E177" t="n">
+        <v>3</v>
+      </c>
+      <c r="F177" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>SignCapricorn</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>2</v>
+      </c>
+      <c r="D178" t="n">
+        <v>50</v>
+      </c>
+      <c r="E178" t="n">
+        <v>3</v>
+      </c>
+      <c r="F178" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>SignCapricorn</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>2</v>
+      </c>
+      <c r="D179" t="n">
+        <v>75</v>
+      </c>
+      <c r="E179" t="n">
+        <v>3</v>
+      </c>
+      <c r="F179" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>SignCapricorn</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>2</v>
+      </c>
+      <c r="D180" t="n">
+        <v>100</v>
+      </c>
+      <c r="E180" t="n">
+        <v>3</v>
+      </c>
+      <c r="F180" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>SignCapricorn</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>3</v>
+      </c>
+      <c r="D181" t="n">
+        <v>0</v>
+      </c>
+      <c r="E181" t="n">
+        <v>3</v>
+      </c>
+      <c r="F181" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>SignCapricorn</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>3</v>
+      </c>
+      <c r="D182" t="n">
+        <v>25</v>
+      </c>
+      <c r="E182" t="n">
+        <v>3</v>
+      </c>
+      <c r="F182" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>SignCapricorn</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>3</v>
+      </c>
+      <c r="D183" t="n">
+        <v>50</v>
+      </c>
+      <c r="E183" t="n">
+        <v>3</v>
+      </c>
+      <c r="F183" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>SignCapricorn</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>3</v>
+      </c>
+      <c r="D184" t="n">
+        <v>75</v>
+      </c>
+      <c r="E184" t="n">
+        <v>3</v>
+      </c>
+      <c r="F184" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>SignCapricorn</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>3</v>
+      </c>
+      <c r="D185" t="n">
+        <v>100</v>
+      </c>
+      <c r="E185" t="n">
+        <v>3</v>
+      </c>
+      <c r="F185" t="n">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>SignAquarius</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>1</v>
+      </c>
+      <c r="D186" t="n">
+        <v>0</v>
+      </c>
+      <c r="E186" t="n">
+        <v>3</v>
+      </c>
+      <c r="F186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>SignAquarius</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>1</v>
+      </c>
+      <c r="D187" t="n">
+        <v>25</v>
+      </c>
+      <c r="E187" t="n">
+        <v>3</v>
+      </c>
+      <c r="F187" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>SignAquarius</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>1</v>
+      </c>
+      <c r="D188" t="n">
+        <v>50</v>
+      </c>
+      <c r="E188" t="n">
+        <v>3</v>
+      </c>
+      <c r="F188" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>SignAquarius</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>1</v>
+      </c>
+      <c r="D189" t="n">
+        <v>75</v>
+      </c>
+      <c r="E189" t="n">
+        <v>3</v>
+      </c>
+      <c r="F189" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>SignAquarius</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>1</v>
+      </c>
+      <c r="D190" t="n">
+        <v>100</v>
+      </c>
+      <c r="E190" t="n">
+        <v>3</v>
+      </c>
+      <c r="F190" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>SignAquarius</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>2</v>
+      </c>
+      <c r="D191" t="n">
+        <v>0</v>
+      </c>
+      <c r="E191" t="n">
+        <v>3</v>
+      </c>
+      <c r="F191" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>SignAquarius</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>2</v>
+      </c>
+      <c r="D192" t="n">
+        <v>25</v>
+      </c>
+      <c r="E192" t="n">
+        <v>3</v>
+      </c>
+      <c r="F192" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>SignAquarius</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>2</v>
+      </c>
+      <c r="D193" t="n">
+        <v>50</v>
+      </c>
+      <c r="E193" t="n">
+        <v>3</v>
+      </c>
+      <c r="F193" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>SignAquarius</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>2</v>
+      </c>
+      <c r="D194" t="n">
+        <v>75</v>
+      </c>
+      <c r="E194" t="n">
+        <v>3</v>
+      </c>
+      <c r="F194" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>SignAquarius</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>2</v>
+      </c>
+      <c r="D195" t="n">
+        <v>100</v>
+      </c>
+      <c r="E195" t="n">
+        <v>3</v>
+      </c>
+      <c r="F195" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>SignAquarius</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>3</v>
+      </c>
+      <c r="D196" t="n">
+        <v>0</v>
+      </c>
+      <c r="E196" t="n">
+        <v>3</v>
+      </c>
+      <c r="F196" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>SignAquarius</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>3</v>
+      </c>
+      <c r="D197" t="n">
+        <v>25</v>
+      </c>
+      <c r="E197" t="n">
+        <v>3</v>
+      </c>
+      <c r="F197" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>SignAquarius</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>3</v>
+      </c>
+      <c r="D198" t="n">
+        <v>50</v>
+      </c>
+      <c r="E198" t="n">
+        <v>3</v>
+      </c>
+      <c r="F198" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>SignAquarius</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>3</v>
+      </c>
+      <c r="D199" t="n">
+        <v>75</v>
+      </c>
+      <c r="E199" t="n">
+        <v>3</v>
+      </c>
+      <c r="F199" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>SignAquarius</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>3</v>
+      </c>
+      <c r="D200" t="n">
+        <v>100</v>
+      </c>
+      <c r="E200" t="n">
+        <v>3</v>
+      </c>
+      <c r="F200" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>SignPisces</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>1</v>
+      </c>
+      <c r="D201" t="n">
+        <v>0</v>
+      </c>
+      <c r="E201" t="n">
+        <v>3</v>
+      </c>
+      <c r="F201" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>SignPisces</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>1</v>
+      </c>
+      <c r="D202" t="n">
+        <v>25</v>
+      </c>
+      <c r="E202" t="n">
+        <v>3</v>
+      </c>
+      <c r="F202" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>SignPisces</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>1</v>
+      </c>
+      <c r="D203" t="n">
+        <v>50</v>
+      </c>
+      <c r="E203" t="n">
+        <v>3</v>
+      </c>
+      <c r="F203" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>SignPisces</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>1</v>
+      </c>
+      <c r="D204" t="n">
+        <v>75</v>
+      </c>
+      <c r="E204" t="n">
+        <v>3</v>
+      </c>
+      <c r="F204" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>SignPisces</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>1</v>
+      </c>
+      <c r="D205" t="n">
+        <v>100</v>
+      </c>
+      <c r="E205" t="n">
+        <v>3</v>
+      </c>
+      <c r="F205" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>SignPisces</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>2</v>
+      </c>
+      <c r="D206" t="n">
+        <v>0</v>
+      </c>
+      <c r="E206" t="n">
+        <v>3</v>
+      </c>
+      <c r="F206" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>SignPisces</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>2</v>
+      </c>
+      <c r="D207" t="n">
+        <v>25</v>
+      </c>
+      <c r="E207" t="n">
+        <v>3</v>
+      </c>
+      <c r="F207" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>SignPisces</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>2</v>
+      </c>
+      <c r="D208" t="n">
+        <v>50</v>
+      </c>
+      <c r="E208" t="n">
+        <v>3</v>
+      </c>
+      <c r="F208" t="n">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>SignPisces</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>2</v>
+      </c>
+      <c r="D209" t="n">
+        <v>75</v>
+      </c>
+      <c r="E209" t="n">
+        <v>3</v>
+      </c>
+      <c r="F209" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>SignPisces</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>2</v>
+      </c>
+      <c r="D210" t="n">
+        <v>100</v>
+      </c>
+      <c r="E210" t="n">
+        <v>3</v>
+      </c>
+      <c r="F210" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>SignPisces</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>3</v>
+      </c>
+      <c r="D211" t="n">
+        <v>0</v>
+      </c>
+      <c r="E211" t="n">
+        <v>3</v>
+      </c>
+      <c r="F211" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>SignPisces</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>3</v>
+      </c>
+      <c r="D212" t="n">
+        <v>25</v>
+      </c>
+      <c r="E212" t="n">
+        <v>3</v>
+      </c>
+      <c r="F212" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>SignPisces</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>3</v>
+      </c>
+      <c r="D213" t="n">
+        <v>50</v>
+      </c>
+      <c r="E213" t="n">
+        <v>3</v>
+      </c>
+      <c r="F213" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>SignPisces</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>3</v>
+      </c>
+      <c r="D214" t="n">
+        <v>75</v>
+      </c>
+      <c r="E214" t="n">
+        <v>3</v>
+      </c>
+      <c r="F214" t="n">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>SignPisces</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>3</v>
+      </c>
+      <c r="D215" t="n">
+        <v>100</v>
+      </c>
+      <c r="E215" t="n">
+        <v>3</v>
+      </c>
+      <c r="F215" t="n">
+        <v>168</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Config/Datas/jingyuan_codex.xlsx
+++ b/Config/Datas/jingyuan_codex.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jingyuan_codex_def" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jingyuan_codex_level" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jingyuan_tune_tier" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tiao_jing_concentration_level" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jingyuan_type_def" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jingyuan_type_pool" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jingyuan_type_info" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jingyuan_premium_essence" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jingyuan_premium_effect" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jingyuan_essence_level_map" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="jingyuan_type_pool_enum" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="named_npc_jingyuan_type" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="jingyuan_codex_def" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="jingyuan_codex_level" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="jingyuan_tune_tier" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="tiao_jing_concentration_level" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="jingyuan_type_def" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="jingyuan_type_pool" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="jingyuan_type_info" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="jingyuan_premium_essence" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="jingyuan_premium_effect" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="jingyuan_essence_level_map" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="jingyuan_type_pool_enum" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="named_npc_jingyuan_type" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="jingyuan_tune_rule" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="jingyuan_renewal_rule" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -27,14 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="21">
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -489,29 +484,32 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
@@ -520,118 +518,115 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1049,11 +1044,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="18.5" customWidth="1" min="3" max="3"/>
+    <col width="15.25" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1187,7 +1183,7 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>orc_common</t>
+          <t>orc_i</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1197,7 +1193,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>orc_common</t>
+          <t>orc_i</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1205,14 +1201,14 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>j_drop_orc_common</t>
+          <t>j_drop_orc_i</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>orc_elite</t>
+          <t>orc_ii</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1222,7 +1218,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>orc_elite</t>
+          <t>orc_ii</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1230,14 +1226,14 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>j_drop_orc_elite</t>
+          <t>j_drop_orc_ii</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>sign_aries</t>
+          <t>human_i</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1247,7 +1243,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>sign_aries</t>
+          <t>human_i</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1255,14 +1251,14 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>j_drop_sign_aries</t>
+          <t>j_drop_human_i</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>sign_taurus</t>
+          <t>human_ii</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1272,7 +1268,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>sign_taurus</t>
+          <t>human_ii</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1280,14 +1276,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>j_drop_sign_taurus</t>
+          <t>j_drop_human_ii</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>sign_gemini</t>
+          <t>human_iii</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1297,7 +1293,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>sign_gemini</t>
+          <t>human_iii</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1305,14 +1301,14 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>j_drop_sign_gemini</t>
+          <t>j_drop_human_iii</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>sign_cancer</t>
+          <t>human_iv</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1322,7 +1318,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>sign_cancer</t>
+          <t>human_iv</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1330,14 +1326,14 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>j_drop_sign_cancer</t>
+          <t>j_drop_human_iv</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>sign_leo</t>
+          <t>human_v</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1347,7 +1343,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>sign_leo</t>
+          <t>human_v</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1355,14 +1351,14 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>j_drop_sign_leo</t>
+          <t>j_drop_human_v</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>sign_virgo</t>
+          <t>human_vi</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1372,7 +1368,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>sign_virgo</t>
+          <t>human_vi</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1380,14 +1376,14 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>j_drop_sign_virgo</t>
+          <t>j_drop_human_vi</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>sign_libra</t>
+          <t>human_vii</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1397,7 +1393,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>sign_libra</t>
+          <t>human_vii</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1405,14 +1401,14 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>j_drop_sign_libra</t>
+          <t>j_drop_human_vii</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>sign_scorpio</t>
+          <t>monster_i</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1422,7 +1418,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>sign_scorpio</t>
+          <t>monster_i</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1430,14 +1426,14 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>j_drop_sign_scorpio</t>
+          <t>j_drop_monster_i</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>sign_sagittarius</t>
+          <t>monster_ii</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1447,7 +1443,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>sign_sagittarius</t>
+          <t>monster_ii</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1455,14 +1451,14 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>j_drop_sign_sagittarius</t>
+          <t>j_drop_monster_ii</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>sign_capricorn</t>
+          <t>monster_iii</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1472,7 +1468,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>sign_capricorn</t>
+          <t>monster_iii</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1480,57 +1476,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>j_drop_sign_capricorn</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>sign_aquarius</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>水瓶座精元</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>sign_aquarius</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>17</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>j_drop_sign_aquarius</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>sign_pisces</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>双鱼座精元</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>sign_pisces</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>18</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>j_drop_sign_pisces</t>
+          <t>j_drop_monster_iii</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1492,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1656,6 +1602,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
@@ -1715,8 +1662,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1826,6 +1773,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" t="n">
         <v>1</v>
@@ -1837,7 +1785,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OrcCommon</t>
+          <t>OrcI</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1855,7 +1803,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OrcElite</t>
+          <t>OrcII</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1873,7 +1821,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SignAries</t>
+          <t>HumanI</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1891,7 +1839,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SignTaurus</t>
+          <t>HumanII</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1909,7 +1857,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SignGemini</t>
+          <t>HumanIII</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1927,7 +1875,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SignCancer</t>
+          <t>HumanIV</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1945,7 +1893,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SignLeo</t>
+          <t>HumanV</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1963,7 +1911,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SignVirgo</t>
+          <t>HumanVI</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1981,7 +1929,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SignLibra</t>
+          <t>HumanVII</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1999,7 +1947,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SignScorpio</t>
+          <t>MonsterI</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2017,7 +1965,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SignSagittarius</t>
+          <t>MonsterII</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2035,46 +1983,10 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SignCapricorn</t>
+          <t>MonsterIII</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="n">
-        <v>13</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>human</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>SignAquarius</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="n">
-        <v>14</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>human</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>SignPisces</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
         <v>100</v>
       </c>
     </row>
@@ -2090,7 +2002,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -2158,6 +2070,562 @@
         <is>
           <t>固定精型枚举</t>
         </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O6"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>rule_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>base_success_rate</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>concentration_diff_rate</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>target_concentration_penalty</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>lower_level_penalty_per_level</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>min_success_rate</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>max_success_rate</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>min_gain</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>max_gain</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>residue_on_failure</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>residue_on_success</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>affix_inherit_rate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>residue_boost_cost</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>residue_boost_success_rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rule key</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Base success rate</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Concentration difference rate</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Target concentration penalty</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lower level penalty</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Minimum success rate</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Maximum success rate</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Minimum gain</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Maximum gain</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Residue on failure</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Residue on success</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Affix inherit rate</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Residue boost cost</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Residue boost success rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>45</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>35</v>
+      </c>
+      <c r="F6" t="n">
+        <v>15</v>
+      </c>
+      <c r="G6" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" t="n">
+        <v>90</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" t="n">
+        <v>12</v>
+      </c>
+      <c r="K6" t="n">
+        <v>12</v>
+      </c>
+      <c r="L6" t="n">
+        <v>6</v>
+      </c>
+      <c r="M6" t="n">
+        <v>35</v>
+      </c>
+      <c r="N6" t="n">
+        <v>20</v>
+      </c>
+      <c r="O6" t="n">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>rule_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>desire_crystal_item_id</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>desire_crystal_cost</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>residue_cost</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>added_shelf_life_days</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>max_renewal_count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Rule key</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Desire crystal item</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Desire crystal cost</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Residue cost</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Added shelf life days</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Maximum renewals</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>desire_crystal_01</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>80</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2171,8 +2639,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col width="21.75" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -2305,7 +2776,7 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>orc_common</t>
+          <t>orc_i</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -2326,7 +2797,7 @@
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>orc_common</t>
+          <t>orc_i</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -2347,7 +2818,7 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>orc_common</t>
+          <t>orc_i</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -2368,7 +2839,7 @@
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>orc_elite</t>
+          <t>orc_ii</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -2389,7 +2860,7 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>orc_elite</t>
+          <t>orc_ii</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2410,7 +2881,7 @@
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>sign_aries</t>
+          <t>human_i</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -2431,7 +2902,7 @@
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>sign_taurus</t>
+          <t>human_ii</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2452,7 +2923,7 @@
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>sign_gemini</t>
+          <t>human_iii</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -2473,7 +2944,7 @@
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>sign_cancer</t>
+          <t>human_iv</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -2494,7 +2965,7 @@
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>sign_leo</t>
+          <t>human_v</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -2515,7 +2986,7 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>sign_virgo</t>
+          <t>human_vi</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -2536,7 +3007,7 @@
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>sign_libra</t>
+          <t>human_vii</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -2557,7 +3028,7 @@
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>sign_scorpio</t>
+          <t>monster_i</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -2578,7 +3049,7 @@
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>sign_sagittarius</t>
+          <t>monster_ii</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -2599,7 +3070,7 @@
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>sign_capricorn</t>
+          <t>monster_iii</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -2612,48 +3083,6 @@
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
-        <is>
-          <t>7,1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>sign_aquarius</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>7,1</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>sign_pisces</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" t="inlineStr">
         <is>
           <t>7,1</t>
         </is>
@@ -2828,7 +3257,7 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>orc_common</t>
+          <t>orc_i</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -2847,7 +3276,7 @@
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>orc_common</t>
+          <t>orc_i</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -2871,7 +3300,7 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>orc_common</t>
+          <t>orc_i</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -2895,7 +3324,7 @@
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>orc_elite</t>
+          <t>orc_ii</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -2914,7 +3343,7 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>orc_elite</t>
+          <t>orc_ii</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -3096,8 +3525,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -3210,7 +3639,7 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>orc_common</t>
+          <t>orc_i</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3220,7 +3649,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>orc_common</t>
+          <t>orc_i</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -3230,7 +3659,7 @@
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>orc_elite</t>
+          <t>orc_ii</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3240,7 +3669,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>orc_elite</t>
+          <t>orc_ii</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -3250,7 +3679,7 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>sign_aries</t>
+          <t>human_i</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3260,7 +3689,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>sign_aries</t>
+          <t>human_i</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -3270,7 +3699,7 @@
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>sign_taurus</t>
+          <t>human_ii</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3280,7 +3709,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>sign_taurus</t>
+          <t>human_ii</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -3290,7 +3719,7 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>sign_gemini</t>
+          <t>human_iii</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3300,7 +3729,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>sign_gemini</t>
+          <t>human_iii</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -3310,7 +3739,7 @@
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>sign_cancer</t>
+          <t>human_iv</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3320,7 +3749,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>sign_cancer</t>
+          <t>human_iv</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -3330,7 +3759,7 @@
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>sign_leo</t>
+          <t>human_v</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3340,7 +3769,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>sign_leo</t>
+          <t>human_v</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -3350,7 +3779,7 @@
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>sign_virgo</t>
+          <t>human_vi</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3360,7 +3789,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>sign_virgo</t>
+          <t>human_vi</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -3370,7 +3799,7 @@
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>sign_libra</t>
+          <t>human_vii</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3380,7 +3809,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>sign_libra</t>
+          <t>human_vii</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -3390,7 +3819,7 @@
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>sign_scorpio</t>
+          <t>monster_i</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3400,7 +3829,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>sign_scorpio</t>
+          <t>monster_i</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -3410,7 +3839,7 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>sign_sagittarius</t>
+          <t>monster_ii</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3420,7 +3849,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>sign_sagittarius</t>
+          <t>monster_ii</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -3430,7 +3859,7 @@
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>sign_capricorn</t>
+          <t>monster_iii</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3440,51 +3869,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>sign_capricorn</t>
+          <t>monster_iii</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>12</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>sign_aquarius</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>水瓶座</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>sign_aquarius</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>sign_pisces</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>双鱼座</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>sign_pisces</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -3498,8 +3887,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -3620,7 +4009,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>orc_common</t>
+          <t>orc_i</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -3638,7 +4027,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>orc_elite</t>
+          <t>orc_ii</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -3656,7 +4045,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>sign_aries</t>
+          <t>human_i</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -3674,7 +4063,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>sign_taurus</t>
+          <t>human_ii</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -3692,7 +4081,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>sign_gemini</t>
+          <t>human_iii</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -3710,7 +4099,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>sign_cancer</t>
+          <t>human_iv</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -3728,7 +4117,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>sign_leo</t>
+          <t>human_v</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -3746,7 +4135,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>sign_virgo</t>
+          <t>human_vi</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -3764,7 +4153,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>sign_libra</t>
+          <t>human_vii</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -3782,7 +4171,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>sign_scorpio</t>
+          <t>monster_i</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -3800,7 +4189,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>sign_sagittarius</t>
+          <t>monster_ii</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -3818,46 +4207,10 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>sign_capricorn</t>
+          <t>monster_iii</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="n">
-        <v>13</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>human</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>sign_aquarius</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="n">
-        <v>14</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>human</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>sign_pisces</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
         <v>100</v>
       </c>
     </row>
@@ -3872,8 +4225,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -4023,15 +4376,16 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>OrcCommon</t>
+          <t>OrcI</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>兽人精元</t>
+          <t>??I</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4046,7 +4400,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>orccommon</t>
+          <t>orci</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -4056,12 +4410,12 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>OrcElite</t>
+          <t>OrcII</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>兽人精英精元</t>
+          <t>??II</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4076,7 +4430,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>orcelite</t>
+          <t>orcii</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -4086,12 +4440,12 @@
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>SignAries</t>
+          <t>HumanI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>白羊座精元</t>
+          <t>??I</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -4106,7 +4460,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>signaries</t>
+          <t>humani</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -4116,12 +4470,12 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>SignTaurus</t>
+          <t>HumanII</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>金牛座精元</t>
+          <t>??II</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -4136,7 +4490,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>signtaurus</t>
+          <t>humanii</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -4146,12 +4500,12 @@
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>SignGemini</t>
+          <t>HumanIII</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>双子座精元</t>
+          <t>??III</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -4166,7 +4520,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>signgemini</t>
+          <t>humaniii</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -4176,12 +4530,12 @@
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>SignCancer</t>
+          <t>HumanIV</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>巨蟹座精元</t>
+          <t>??IV</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4196,7 +4550,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>signcancer</t>
+          <t>humaniv</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -4206,12 +4560,12 @@
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>SignLeo</t>
+          <t>HumanV</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>狮子座精元</t>
+          <t>??V</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -4226,7 +4580,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>signleo</t>
+          <t>humanv</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -4236,12 +4590,12 @@
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>SignVirgo</t>
+          <t>HumanVI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>处女座精元</t>
+          <t>??VI</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -4256,7 +4610,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>signvirgo</t>
+          <t>humanvi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -4266,12 +4620,12 @@
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>SignLibra</t>
+          <t>HumanVII</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>天秤座精元</t>
+          <t>??VII</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -4286,7 +4640,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>signlibra</t>
+          <t>humanvii</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -4296,12 +4650,12 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>SignScorpio</t>
+          <t>MonsterI</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>天蝎座精元</t>
+          <t>??I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4311,12 +4665,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>monster</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>signscorpio</t>
+          <t>monsteri</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -4326,12 +4680,12 @@
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>SignSagittarius</t>
+          <t>MonsterII</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>射手座精元</t>
+          <t>??II</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4341,12 +4695,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>monster</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>signsagittarius</t>
+          <t>monsterii</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -4356,12 +4710,12 @@
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>SignCapricorn</t>
+          <t>MonsterIII</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>摩羯座精元</t>
+          <t>??III</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4371,76 +4725,16 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>human</t>
+          <t>monster</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>signcapricorn</t>
+          <t>monsteriii</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>12</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>SignAquarius</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>水瓶座精元</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>jingyuan/signaquarius</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>human</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>signaquarius</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>SignPisces</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>双鱼座精元</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>jingyuan/signpisces</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>human</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>signpisces</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -4454,8 +4748,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -4605,20 +4899,21 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>premium_orccommon</t>
+          <t>premium_orci</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OrcCommon</t>
+          <t>OrcI</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>优质兽人精元</t>
+          <t>??优质兽人精元</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -4638,17 +4933,17 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>premium_orcelite</t>
+          <t>premium_orcii</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>OrcElite</t>
+          <t>OrcII</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>优质兽人精英精元</t>
+          <t>??优质兽人精英精元</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -4668,17 +4963,17 @@
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>premium_signaries</t>
+          <t>premium_humani</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SignAries</t>
+          <t>HumanI</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>优质白羊座精元</t>
+          <t>??优质白羊座精元</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -4698,17 +4993,17 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>premium_signtaurus</t>
+          <t>premium_humanii</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SignTaurus</t>
+          <t>HumanII</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>优质金牛座精元</t>
+          <t>??优质金牛座精元</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -4728,17 +5023,17 @@
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>premium_signgemini</t>
+          <t>premium_humaniii</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SignGemini</t>
+          <t>HumanIII</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>优质双子座精元</t>
+          <t>??优质双子座精元</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -4758,17 +5053,17 @@
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>premium_signcancer</t>
+          <t>premium_humaniv</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SignCancer</t>
+          <t>HumanIV</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>优质巨蟹座精元</t>
+          <t>??优质巨蟹座精元</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -4788,17 +5083,17 @@
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>premium_signleo</t>
+          <t>premium_humanv</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SignLeo</t>
+          <t>HumanV</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>优质狮子座精元</t>
+          <t>??优质狮子座精元</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -4818,17 +5113,17 @@
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>premium_signvirgo</t>
+          <t>premium_humanvi</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SignVirgo</t>
+          <t>HumanVI</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>优质处女座精元</t>
+          <t>??优质处女座精元</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -4848,17 +5143,17 @@
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>premium_signlibra</t>
+          <t>premium_humanvii</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SignLibra</t>
+          <t>HumanVII</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>优质天秤座精元</t>
+          <t>??优质天秤座精元</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -4878,17 +5173,17 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>premium_signscorpio</t>
+          <t>premium_monsteri</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SignScorpio</t>
+          <t>MonsterI</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>优质天蝎座精元</t>
+          <t>??优质天蝎座精元</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -4908,17 +5203,17 @@
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>premium_signsagittarius</t>
+          <t>premium_monsterii</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SignSagittarius</t>
+          <t>MonsterII</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>优质射手座精元</t>
+          <t>??优质射手座精元</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -4938,17 +5233,17 @@
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>premium_signcapricorn</t>
+          <t>premium_monsteriii</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SignCapricorn</t>
+          <t>MonsterIII</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>优质摩羯座精元</t>
+          <t>??优质摩羯座精元</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -4960,66 +5255,6 @@
         </is>
       </c>
       <c r="G17" t="inlineStr">
-        <is>
-          <t>extract_or_event</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>premium_signaquarius</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>SignAquarius</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>优质水瓶座精元</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>affix_signaquarius</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>extract_or_event</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>premium_signpisces</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>SignPisces</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>优质双鱼座精元</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>3</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>affix_signpisces</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
         <is>
           <t>extract_or_event</t>
         </is>
@@ -5036,8 +5271,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F215"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F185"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -5162,10 +5397,11 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>OrcCommon</t>
+          <t>OrcI</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -5184,7 +5420,7 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>OrcCommon</t>
+          <t>OrcI</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -5203,7 +5439,7 @@
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>OrcCommon</t>
+          <t>OrcI</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -5222,7 +5458,7 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>OrcCommon</t>
+          <t>OrcI</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5241,7 +5477,7 @@
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>OrcCommon</t>
+          <t>OrcI</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -5260,7 +5496,7 @@
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>OrcCommon</t>
+          <t>OrcI</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -5279,7 +5515,7 @@
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>OrcCommon</t>
+          <t>OrcI</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -5298,7 +5534,7 @@
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>OrcCommon</t>
+          <t>OrcI</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -5317,7 +5553,7 @@
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>OrcCommon</t>
+          <t>OrcI</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -5336,7 +5572,7 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>OrcCommon</t>
+          <t>OrcI</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -5355,7 +5591,7 @@
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>OrcCommon</t>
+          <t>OrcI</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -5374,7 +5610,7 @@
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>OrcCommon</t>
+          <t>OrcI</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -5393,7 +5629,7 @@
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>OrcCommon</t>
+          <t>OrcI</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -5412,7 +5648,7 @@
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>OrcCommon</t>
+          <t>OrcI</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -5431,7 +5667,7 @@
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>OrcCommon</t>
+          <t>OrcI</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -5450,7 +5686,7 @@
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>OrcElite</t>
+          <t>OrcII</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -5469,7 +5705,7 @@
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>OrcElite</t>
+          <t>OrcII</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -5488,7 +5724,7 @@
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>OrcElite</t>
+          <t>OrcII</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -5507,7 +5743,7 @@
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>OrcElite</t>
+          <t>OrcII</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -5526,7 +5762,7 @@
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>OrcElite</t>
+          <t>OrcII</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -5545,7 +5781,7 @@
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>OrcElite</t>
+          <t>OrcII</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -5564,7 +5800,7 @@
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>OrcElite</t>
+          <t>OrcII</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -5583,7 +5819,7 @@
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>OrcElite</t>
+          <t>OrcII</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -5602,7 +5838,7 @@
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
-          <t>OrcElite</t>
+          <t>OrcII</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -5621,7 +5857,7 @@
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>OrcElite</t>
+          <t>OrcII</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -5640,7 +5876,7 @@
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
-          <t>OrcElite</t>
+          <t>OrcII</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -5659,7 +5895,7 @@
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
-          <t>OrcElite</t>
+          <t>OrcII</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -5678,7 +5914,7 @@
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
-          <t>OrcElite</t>
+          <t>OrcII</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -5697,7 +5933,7 @@
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>OrcElite</t>
+          <t>OrcII</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -5716,7 +5952,7 @@
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t>OrcElite</t>
+          <t>OrcII</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -5735,7 +5971,7 @@
     <row r="36">
       <c r="B36" t="inlineStr">
         <is>
-          <t>SignAries</t>
+          <t>HumanI</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -5754,7 +5990,7 @@
     <row r="37">
       <c r="B37" t="inlineStr">
         <is>
-          <t>SignAries</t>
+          <t>HumanI</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -5773,7 +6009,7 @@
     <row r="38">
       <c r="B38" t="inlineStr">
         <is>
-          <t>SignAries</t>
+          <t>HumanI</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -5792,7 +6028,7 @@
     <row r="39">
       <c r="B39" t="inlineStr">
         <is>
-          <t>SignAries</t>
+          <t>HumanI</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -5811,7 +6047,7 @@
     <row r="40">
       <c r="B40" t="inlineStr">
         <is>
-          <t>SignAries</t>
+          <t>HumanI</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5830,7 +6066,7 @@
     <row r="41">
       <c r="B41" t="inlineStr">
         <is>
-          <t>SignAries</t>
+          <t>HumanI</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5849,7 +6085,7 @@
     <row r="42">
       <c r="B42" t="inlineStr">
         <is>
-          <t>SignAries</t>
+          <t>HumanI</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -5868,7 +6104,7 @@
     <row r="43">
       <c r="B43" t="inlineStr">
         <is>
-          <t>SignAries</t>
+          <t>HumanI</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5887,7 +6123,7 @@
     <row r="44">
       <c r="B44" t="inlineStr">
         <is>
-          <t>SignAries</t>
+          <t>HumanI</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5906,7 +6142,7 @@
     <row r="45">
       <c r="B45" t="inlineStr">
         <is>
-          <t>SignAries</t>
+          <t>HumanI</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -5925,7 +6161,7 @@
     <row r="46">
       <c r="B46" t="inlineStr">
         <is>
-          <t>SignAries</t>
+          <t>HumanI</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5944,7 +6180,7 @@
     <row r="47">
       <c r="B47" t="inlineStr">
         <is>
-          <t>SignAries</t>
+          <t>HumanI</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -5963,7 +6199,7 @@
     <row r="48">
       <c r="B48" t="inlineStr">
         <is>
-          <t>SignAries</t>
+          <t>HumanI</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -5982,7 +6218,7 @@
     <row r="49">
       <c r="B49" t="inlineStr">
         <is>
-          <t>SignAries</t>
+          <t>HumanI</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6001,7 +6237,7 @@
     <row r="50">
       <c r="B50" t="inlineStr">
         <is>
-          <t>SignAries</t>
+          <t>HumanI</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6020,7 +6256,7 @@
     <row r="51">
       <c r="B51" t="inlineStr">
         <is>
-          <t>SignTaurus</t>
+          <t>HumanII</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6039,7 +6275,7 @@
     <row r="52">
       <c r="B52" t="inlineStr">
         <is>
-          <t>SignTaurus</t>
+          <t>HumanII</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -6058,7 +6294,7 @@
     <row r="53">
       <c r="B53" t="inlineStr">
         <is>
-          <t>SignTaurus</t>
+          <t>HumanII</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -6077,7 +6313,7 @@
     <row r="54">
       <c r="B54" t="inlineStr">
         <is>
-          <t>SignTaurus</t>
+          <t>HumanII</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -6096,7 +6332,7 @@
     <row r="55">
       <c r="B55" t="inlineStr">
         <is>
-          <t>SignTaurus</t>
+          <t>HumanII</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -6115,7 +6351,7 @@
     <row r="56">
       <c r="B56" t="inlineStr">
         <is>
-          <t>SignTaurus</t>
+          <t>HumanII</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -6134,7 +6370,7 @@
     <row r="57">
       <c r="B57" t="inlineStr">
         <is>
-          <t>SignTaurus</t>
+          <t>HumanII</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -6153,7 +6389,7 @@
     <row r="58">
       <c r="B58" t="inlineStr">
         <is>
-          <t>SignTaurus</t>
+          <t>HumanII</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -6172,7 +6408,7 @@
     <row r="59">
       <c r="B59" t="inlineStr">
         <is>
-          <t>SignTaurus</t>
+          <t>HumanII</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -6191,7 +6427,7 @@
     <row r="60">
       <c r="B60" t="inlineStr">
         <is>
-          <t>SignTaurus</t>
+          <t>HumanII</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -6210,7 +6446,7 @@
     <row r="61">
       <c r="B61" t="inlineStr">
         <is>
-          <t>SignTaurus</t>
+          <t>HumanII</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -6229,7 +6465,7 @@
     <row r="62">
       <c r="B62" t="inlineStr">
         <is>
-          <t>SignTaurus</t>
+          <t>HumanII</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -6248,7 +6484,7 @@
     <row r="63">
       <c r="B63" t="inlineStr">
         <is>
-          <t>SignTaurus</t>
+          <t>HumanII</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -6267,7 +6503,7 @@
     <row r="64">
       <c r="B64" t="inlineStr">
         <is>
-          <t>SignTaurus</t>
+          <t>HumanII</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -6286,7 +6522,7 @@
     <row r="65">
       <c r="B65" t="inlineStr">
         <is>
-          <t>SignTaurus</t>
+          <t>HumanII</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -6305,7 +6541,7 @@
     <row r="66">
       <c r="B66" t="inlineStr">
         <is>
-          <t>SignGemini</t>
+          <t>HumanIII</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -6324,7 +6560,7 @@
     <row r="67">
       <c r="B67" t="inlineStr">
         <is>
-          <t>SignGemini</t>
+          <t>HumanIII</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -6343,7 +6579,7 @@
     <row r="68">
       <c r="B68" t="inlineStr">
         <is>
-          <t>SignGemini</t>
+          <t>HumanIII</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -6362,7 +6598,7 @@
     <row r="69">
       <c r="B69" t="inlineStr">
         <is>
-          <t>SignGemini</t>
+          <t>HumanIII</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -6381,7 +6617,7 @@
     <row r="70">
       <c r="B70" t="inlineStr">
         <is>
-          <t>SignGemini</t>
+          <t>HumanIII</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -6400,7 +6636,7 @@
     <row r="71">
       <c r="B71" t="inlineStr">
         <is>
-          <t>SignGemini</t>
+          <t>HumanIII</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -6419,7 +6655,7 @@
     <row r="72">
       <c r="B72" t="inlineStr">
         <is>
-          <t>SignGemini</t>
+          <t>HumanIII</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -6438,7 +6674,7 @@
     <row r="73">
       <c r="B73" t="inlineStr">
         <is>
-          <t>SignGemini</t>
+          <t>HumanIII</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -6457,7 +6693,7 @@
     <row r="74">
       <c r="B74" t="inlineStr">
         <is>
-          <t>SignGemini</t>
+          <t>HumanIII</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -6476,7 +6712,7 @@
     <row r="75">
       <c r="B75" t="inlineStr">
         <is>
-          <t>SignGemini</t>
+          <t>HumanIII</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -6495,7 +6731,7 @@
     <row r="76">
       <c r="B76" t="inlineStr">
         <is>
-          <t>SignGemini</t>
+          <t>HumanIII</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -6514,7 +6750,7 @@
     <row r="77">
       <c r="B77" t="inlineStr">
         <is>
-          <t>SignGemini</t>
+          <t>HumanIII</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -6533,7 +6769,7 @@
     <row r="78">
       <c r="B78" t="inlineStr">
         <is>
-          <t>SignGemini</t>
+          <t>HumanIII</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -6552,7 +6788,7 @@
     <row r="79">
       <c r="B79" t="inlineStr">
         <is>
-          <t>SignGemini</t>
+          <t>HumanIII</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -6571,7 +6807,7 @@
     <row r="80">
       <c r="B80" t="inlineStr">
         <is>
-          <t>SignGemini</t>
+          <t>HumanIII</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -6590,7 +6826,7 @@
     <row r="81">
       <c r="B81" t="inlineStr">
         <is>
-          <t>SignCancer</t>
+          <t>HumanIV</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -6609,7 +6845,7 @@
     <row r="82">
       <c r="B82" t="inlineStr">
         <is>
-          <t>SignCancer</t>
+          <t>HumanIV</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -6628,7 +6864,7 @@
     <row r="83">
       <c r="B83" t="inlineStr">
         <is>
-          <t>SignCancer</t>
+          <t>HumanIV</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -6647,7 +6883,7 @@
     <row r="84">
       <c r="B84" t="inlineStr">
         <is>
-          <t>SignCancer</t>
+          <t>HumanIV</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -6666,7 +6902,7 @@
     <row r="85">
       <c r="B85" t="inlineStr">
         <is>
-          <t>SignCancer</t>
+          <t>HumanIV</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -6685,7 +6921,7 @@
     <row r="86">
       <c r="B86" t="inlineStr">
         <is>
-          <t>SignCancer</t>
+          <t>HumanIV</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -6704,7 +6940,7 @@
     <row r="87">
       <c r="B87" t="inlineStr">
         <is>
-          <t>SignCancer</t>
+          <t>HumanIV</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -6723,7 +6959,7 @@
     <row r="88">
       <c r="B88" t="inlineStr">
         <is>
-          <t>SignCancer</t>
+          <t>HumanIV</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -6742,7 +6978,7 @@
     <row r="89">
       <c r="B89" t="inlineStr">
         <is>
-          <t>SignCancer</t>
+          <t>HumanIV</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -6761,7 +6997,7 @@
     <row r="90">
       <c r="B90" t="inlineStr">
         <is>
-          <t>SignCancer</t>
+          <t>HumanIV</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -6780,7 +7016,7 @@
     <row r="91">
       <c r="B91" t="inlineStr">
         <is>
-          <t>SignCancer</t>
+          <t>HumanIV</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -6799,7 +7035,7 @@
     <row r="92">
       <c r="B92" t="inlineStr">
         <is>
-          <t>SignCancer</t>
+          <t>HumanIV</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -6818,7 +7054,7 @@
     <row r="93">
       <c r="B93" t="inlineStr">
         <is>
-          <t>SignCancer</t>
+          <t>HumanIV</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -6837,7 +7073,7 @@
     <row r="94">
       <c r="B94" t="inlineStr">
         <is>
-          <t>SignCancer</t>
+          <t>HumanIV</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -6856,7 +7092,7 @@
     <row r="95">
       <c r="B95" t="inlineStr">
         <is>
-          <t>SignCancer</t>
+          <t>HumanIV</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -6875,7 +7111,7 @@
     <row r="96">
       <c r="B96" t="inlineStr">
         <is>
-          <t>SignLeo</t>
+          <t>HumanV</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -6894,7 +7130,7 @@
     <row r="97">
       <c r="B97" t="inlineStr">
         <is>
-          <t>SignLeo</t>
+          <t>HumanV</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -6913,7 +7149,7 @@
     <row r="98">
       <c r="B98" t="inlineStr">
         <is>
-          <t>SignLeo</t>
+          <t>HumanV</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -6932,7 +7168,7 @@
     <row r="99">
       <c r="B99" t="inlineStr">
         <is>
-          <t>SignLeo</t>
+          <t>HumanV</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -6951,7 +7187,7 @@
     <row r="100">
       <c r="B100" t="inlineStr">
         <is>
-          <t>SignLeo</t>
+          <t>HumanV</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -6970,7 +7206,7 @@
     <row r="101">
       <c r="B101" t="inlineStr">
         <is>
-          <t>SignLeo</t>
+          <t>HumanV</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -6989,7 +7225,7 @@
     <row r="102">
       <c r="B102" t="inlineStr">
         <is>
-          <t>SignLeo</t>
+          <t>HumanV</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -7008,7 +7244,7 @@
     <row r="103">
       <c r="B103" t="inlineStr">
         <is>
-          <t>SignLeo</t>
+          <t>HumanV</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -7027,7 +7263,7 @@
     <row r="104">
       <c r="B104" t="inlineStr">
         <is>
-          <t>SignLeo</t>
+          <t>HumanV</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -7046,7 +7282,7 @@
     <row r="105">
       <c r="B105" t="inlineStr">
         <is>
-          <t>SignLeo</t>
+          <t>HumanV</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -7065,7 +7301,7 @@
     <row r="106">
       <c r="B106" t="inlineStr">
         <is>
-          <t>SignLeo</t>
+          <t>HumanV</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -7084,7 +7320,7 @@
     <row r="107">
       <c r="B107" t="inlineStr">
         <is>
-          <t>SignLeo</t>
+          <t>HumanV</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -7103,7 +7339,7 @@
     <row r="108">
       <c r="B108" t="inlineStr">
         <is>
-          <t>SignLeo</t>
+          <t>HumanV</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -7122,7 +7358,7 @@
     <row r="109">
       <c r="B109" t="inlineStr">
         <is>
-          <t>SignLeo</t>
+          <t>HumanV</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -7141,7 +7377,7 @@
     <row r="110">
       <c r="B110" t="inlineStr">
         <is>
-          <t>SignLeo</t>
+          <t>HumanV</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -7160,7 +7396,7 @@
     <row r="111">
       <c r="B111" t="inlineStr">
         <is>
-          <t>SignVirgo</t>
+          <t>HumanVI</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -7179,7 +7415,7 @@
     <row r="112">
       <c r="B112" t="inlineStr">
         <is>
-          <t>SignVirgo</t>
+          <t>HumanVI</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -7198,7 +7434,7 @@
     <row r="113">
       <c r="B113" t="inlineStr">
         <is>
-          <t>SignVirgo</t>
+          <t>HumanVI</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -7217,7 +7453,7 @@
     <row r="114">
       <c r="B114" t="inlineStr">
         <is>
-          <t>SignVirgo</t>
+          <t>HumanVI</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -7236,7 +7472,7 @@
     <row r="115">
       <c r="B115" t="inlineStr">
         <is>
-          <t>SignVirgo</t>
+          <t>HumanVI</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -7255,7 +7491,7 @@
     <row r="116">
       <c r="B116" t="inlineStr">
         <is>
-          <t>SignVirgo</t>
+          <t>HumanVI</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -7274,7 +7510,7 @@
     <row r="117">
       <c r="B117" t="inlineStr">
         <is>
-          <t>SignVirgo</t>
+          <t>HumanVI</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -7293,7 +7529,7 @@
     <row r="118">
       <c r="B118" t="inlineStr">
         <is>
-          <t>SignVirgo</t>
+          <t>HumanVI</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -7312,7 +7548,7 @@
     <row r="119">
       <c r="B119" t="inlineStr">
         <is>
-          <t>SignVirgo</t>
+          <t>HumanVI</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -7331,7 +7567,7 @@
     <row r="120">
       <c r="B120" t="inlineStr">
         <is>
-          <t>SignVirgo</t>
+          <t>HumanVI</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -7350,7 +7586,7 @@
     <row r="121">
       <c r="B121" t="inlineStr">
         <is>
-          <t>SignVirgo</t>
+          <t>HumanVI</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -7369,7 +7605,7 @@
     <row r="122">
       <c r="B122" t="inlineStr">
         <is>
-          <t>SignVirgo</t>
+          <t>HumanVI</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -7388,7 +7624,7 @@
     <row r="123">
       <c r="B123" t="inlineStr">
         <is>
-          <t>SignVirgo</t>
+          <t>HumanVI</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -7407,7 +7643,7 @@
     <row r="124">
       <c r="B124" t="inlineStr">
         <is>
-          <t>SignVirgo</t>
+          <t>HumanVI</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -7426,7 +7662,7 @@
     <row r="125">
       <c r="B125" t="inlineStr">
         <is>
-          <t>SignVirgo</t>
+          <t>HumanVI</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -7445,7 +7681,7 @@
     <row r="126">
       <c r="B126" t="inlineStr">
         <is>
-          <t>SignLibra</t>
+          <t>HumanVII</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -7464,7 +7700,7 @@
     <row r="127">
       <c r="B127" t="inlineStr">
         <is>
-          <t>SignLibra</t>
+          <t>HumanVII</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -7483,7 +7719,7 @@
     <row r="128">
       <c r="B128" t="inlineStr">
         <is>
-          <t>SignLibra</t>
+          <t>HumanVII</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -7502,7 +7738,7 @@
     <row r="129">
       <c r="B129" t="inlineStr">
         <is>
-          <t>SignLibra</t>
+          <t>HumanVII</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -7521,7 +7757,7 @@
     <row r="130">
       <c r="B130" t="inlineStr">
         <is>
-          <t>SignLibra</t>
+          <t>HumanVII</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -7540,7 +7776,7 @@
     <row r="131">
       <c r="B131" t="inlineStr">
         <is>
-          <t>SignLibra</t>
+          <t>HumanVII</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -7559,7 +7795,7 @@
     <row r="132">
       <c r="B132" t="inlineStr">
         <is>
-          <t>SignLibra</t>
+          <t>HumanVII</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -7578,7 +7814,7 @@
     <row r="133">
       <c r="B133" t="inlineStr">
         <is>
-          <t>SignLibra</t>
+          <t>HumanVII</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -7597,7 +7833,7 @@
     <row r="134">
       <c r="B134" t="inlineStr">
         <is>
-          <t>SignLibra</t>
+          <t>HumanVII</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -7616,7 +7852,7 @@
     <row r="135">
       <c r="B135" t="inlineStr">
         <is>
-          <t>SignLibra</t>
+          <t>HumanVII</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -7635,7 +7871,7 @@
     <row r="136">
       <c r="B136" t="inlineStr">
         <is>
-          <t>SignLibra</t>
+          <t>HumanVII</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -7654,7 +7890,7 @@
     <row r="137">
       <c r="B137" t="inlineStr">
         <is>
-          <t>SignLibra</t>
+          <t>HumanVII</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -7673,7 +7909,7 @@
     <row r="138">
       <c r="B138" t="inlineStr">
         <is>
-          <t>SignLibra</t>
+          <t>HumanVII</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -7692,7 +7928,7 @@
     <row r="139">
       <c r="B139" t="inlineStr">
         <is>
-          <t>SignLibra</t>
+          <t>HumanVII</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -7711,7 +7947,7 @@
     <row r="140">
       <c r="B140" t="inlineStr">
         <is>
-          <t>SignLibra</t>
+          <t>HumanVII</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -7730,7 +7966,7 @@
     <row r="141">
       <c r="B141" t="inlineStr">
         <is>
-          <t>SignScorpio</t>
+          <t>MonsterI</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -7749,7 +7985,7 @@
     <row r="142">
       <c r="B142" t="inlineStr">
         <is>
-          <t>SignScorpio</t>
+          <t>MonsterI</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -7768,7 +8004,7 @@
     <row r="143">
       <c r="B143" t="inlineStr">
         <is>
-          <t>SignScorpio</t>
+          <t>MonsterI</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -7787,7 +8023,7 @@
     <row r="144">
       <c r="B144" t="inlineStr">
         <is>
-          <t>SignScorpio</t>
+          <t>MonsterI</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -7806,7 +8042,7 @@
     <row r="145">
       <c r="B145" t="inlineStr">
         <is>
-          <t>SignScorpio</t>
+          <t>MonsterI</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -7825,7 +8061,7 @@
     <row r="146">
       <c r="B146" t="inlineStr">
         <is>
-          <t>SignScorpio</t>
+          <t>MonsterI</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -7844,7 +8080,7 @@
     <row r="147">
       <c r="B147" t="inlineStr">
         <is>
-          <t>SignScorpio</t>
+          <t>MonsterI</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -7863,7 +8099,7 @@
     <row r="148">
       <c r="B148" t="inlineStr">
         <is>
-          <t>SignScorpio</t>
+          <t>MonsterI</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -7882,7 +8118,7 @@
     <row r="149">
       <c r="B149" t="inlineStr">
         <is>
-          <t>SignScorpio</t>
+          <t>MonsterI</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -7901,7 +8137,7 @@
     <row r="150">
       <c r="B150" t="inlineStr">
         <is>
-          <t>SignScorpio</t>
+          <t>MonsterI</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -7920,7 +8156,7 @@
     <row r="151">
       <c r="B151" t="inlineStr">
         <is>
-          <t>SignScorpio</t>
+          <t>MonsterI</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -7939,7 +8175,7 @@
     <row r="152">
       <c r="B152" t="inlineStr">
         <is>
-          <t>SignScorpio</t>
+          <t>MonsterI</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -7958,7 +8194,7 @@
     <row r="153">
       <c r="B153" t="inlineStr">
         <is>
-          <t>SignScorpio</t>
+          <t>MonsterI</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -7977,7 +8213,7 @@
     <row r="154">
       <c r="B154" t="inlineStr">
         <is>
-          <t>SignScorpio</t>
+          <t>MonsterI</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -7996,7 +8232,7 @@
     <row r="155">
       <c r="B155" t="inlineStr">
         <is>
-          <t>SignScorpio</t>
+          <t>MonsterI</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -8015,7 +8251,7 @@
     <row r="156">
       <c r="B156" t="inlineStr">
         <is>
-          <t>SignSagittarius</t>
+          <t>MonsterII</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -8034,7 +8270,7 @@
     <row r="157">
       <c r="B157" t="inlineStr">
         <is>
-          <t>SignSagittarius</t>
+          <t>MonsterII</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -8053,7 +8289,7 @@
     <row r="158">
       <c r="B158" t="inlineStr">
         <is>
-          <t>SignSagittarius</t>
+          <t>MonsterII</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -8072,7 +8308,7 @@
     <row r="159">
       <c r="B159" t="inlineStr">
         <is>
-          <t>SignSagittarius</t>
+          <t>MonsterII</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -8091,7 +8327,7 @@
     <row r="160">
       <c r="B160" t="inlineStr">
         <is>
-          <t>SignSagittarius</t>
+          <t>MonsterII</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -8110,7 +8346,7 @@
     <row r="161">
       <c r="B161" t="inlineStr">
         <is>
-          <t>SignSagittarius</t>
+          <t>MonsterII</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -8129,7 +8365,7 @@
     <row r="162">
       <c r="B162" t="inlineStr">
         <is>
-          <t>SignSagittarius</t>
+          <t>MonsterII</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -8148,7 +8384,7 @@
     <row r="163">
       <c r="B163" t="inlineStr">
         <is>
-          <t>SignSagittarius</t>
+          <t>MonsterII</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -8167,7 +8403,7 @@
     <row r="164">
       <c r="B164" t="inlineStr">
         <is>
-          <t>SignSagittarius</t>
+          <t>MonsterII</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -8186,7 +8422,7 @@
     <row r="165">
       <c r="B165" t="inlineStr">
         <is>
-          <t>SignSagittarius</t>
+          <t>MonsterII</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -8205,7 +8441,7 @@
     <row r="166">
       <c r="B166" t="inlineStr">
         <is>
-          <t>SignSagittarius</t>
+          <t>MonsterII</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -8224,7 +8460,7 @@
     <row r="167">
       <c r="B167" t="inlineStr">
         <is>
-          <t>SignSagittarius</t>
+          <t>MonsterII</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -8243,7 +8479,7 @@
     <row r="168">
       <c r="B168" t="inlineStr">
         <is>
-          <t>SignSagittarius</t>
+          <t>MonsterII</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -8262,7 +8498,7 @@
     <row r="169">
       <c r="B169" t="inlineStr">
         <is>
-          <t>SignSagittarius</t>
+          <t>MonsterII</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -8281,7 +8517,7 @@
     <row r="170">
       <c r="B170" t="inlineStr">
         <is>
-          <t>SignSagittarius</t>
+          <t>MonsterII</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -8300,7 +8536,7 @@
     <row r="171">
       <c r="B171" t="inlineStr">
         <is>
-          <t>SignCapricorn</t>
+          <t>MonsterIII</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -8319,7 +8555,7 @@
     <row r="172">
       <c r="B172" t="inlineStr">
         <is>
-          <t>SignCapricorn</t>
+          <t>MonsterIII</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -8338,7 +8574,7 @@
     <row r="173">
       <c r="B173" t="inlineStr">
         <is>
-          <t>SignCapricorn</t>
+          <t>MonsterIII</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -8357,7 +8593,7 @@
     <row r="174">
       <c r="B174" t="inlineStr">
         <is>
-          <t>SignCapricorn</t>
+          <t>MonsterIII</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -8376,7 +8612,7 @@
     <row r="175">
       <c r="B175" t="inlineStr">
         <is>
-          <t>SignCapricorn</t>
+          <t>MonsterIII</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -8395,7 +8631,7 @@
     <row r="176">
       <c r="B176" t="inlineStr">
         <is>
-          <t>SignCapricorn</t>
+          <t>MonsterIII</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -8414,7 +8650,7 @@
     <row r="177">
       <c r="B177" t="inlineStr">
         <is>
-          <t>SignCapricorn</t>
+          <t>MonsterIII</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -8433,7 +8669,7 @@
     <row r="178">
       <c r="B178" t="inlineStr">
         <is>
-          <t>SignCapricorn</t>
+          <t>MonsterIII</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -8452,7 +8688,7 @@
     <row r="179">
       <c r="B179" t="inlineStr">
         <is>
-          <t>SignCapricorn</t>
+          <t>MonsterIII</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -8471,7 +8707,7 @@
     <row r="180">
       <c r="B180" t="inlineStr">
         <is>
-          <t>SignCapricorn</t>
+          <t>MonsterIII</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -8490,7 +8726,7 @@
     <row r="181">
       <c r="B181" t="inlineStr">
         <is>
-          <t>SignCapricorn</t>
+          <t>MonsterIII</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -8509,7 +8745,7 @@
     <row r="182">
       <c r="B182" t="inlineStr">
         <is>
-          <t>SignCapricorn</t>
+          <t>MonsterIII</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -8528,7 +8764,7 @@
     <row r="183">
       <c r="B183" t="inlineStr">
         <is>
-          <t>SignCapricorn</t>
+          <t>MonsterIII</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -8547,7 +8783,7 @@
     <row r="184">
       <c r="B184" t="inlineStr">
         <is>
-          <t>SignCapricorn</t>
+          <t>MonsterIII</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -8566,7 +8802,7 @@
     <row r="185">
       <c r="B185" t="inlineStr">
         <is>
-          <t>SignCapricorn</t>
+          <t>MonsterIII</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -8580,576 +8816,6 @@
       </c>
       <c r="F185" t="n">
         <v>144</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>SignAquarius</t>
-        </is>
-      </c>
-      <c r="C186" t="n">
-        <v>1</v>
-      </c>
-      <c r="D186" t="n">
-        <v>0</v>
-      </c>
-      <c r="E186" t="n">
-        <v>3</v>
-      </c>
-      <c r="F186" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>SignAquarius</t>
-        </is>
-      </c>
-      <c r="C187" t="n">
-        <v>1</v>
-      </c>
-      <c r="D187" t="n">
-        <v>25</v>
-      </c>
-      <c r="E187" t="n">
-        <v>3</v>
-      </c>
-      <c r="F187" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>SignAquarius</t>
-        </is>
-      </c>
-      <c r="C188" t="n">
-        <v>1</v>
-      </c>
-      <c r="D188" t="n">
-        <v>50</v>
-      </c>
-      <c r="E188" t="n">
-        <v>3</v>
-      </c>
-      <c r="F188" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>SignAquarius</t>
-        </is>
-      </c>
-      <c r="C189" t="n">
-        <v>1</v>
-      </c>
-      <c r="D189" t="n">
-        <v>75</v>
-      </c>
-      <c r="E189" t="n">
-        <v>3</v>
-      </c>
-      <c r="F189" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>SignAquarius</t>
-        </is>
-      </c>
-      <c r="C190" t="n">
-        <v>1</v>
-      </c>
-      <c r="D190" t="n">
-        <v>100</v>
-      </c>
-      <c r="E190" t="n">
-        <v>3</v>
-      </c>
-      <c r="F190" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>SignAquarius</t>
-        </is>
-      </c>
-      <c r="C191" t="n">
-        <v>2</v>
-      </c>
-      <c r="D191" t="n">
-        <v>0</v>
-      </c>
-      <c r="E191" t="n">
-        <v>3</v>
-      </c>
-      <c r="F191" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>SignAquarius</t>
-        </is>
-      </c>
-      <c r="C192" t="n">
-        <v>2</v>
-      </c>
-      <c r="D192" t="n">
-        <v>25</v>
-      </c>
-      <c r="E192" t="n">
-        <v>3</v>
-      </c>
-      <c r="F192" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>SignAquarius</t>
-        </is>
-      </c>
-      <c r="C193" t="n">
-        <v>2</v>
-      </c>
-      <c r="D193" t="n">
-        <v>50</v>
-      </c>
-      <c r="E193" t="n">
-        <v>3</v>
-      </c>
-      <c r="F193" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>SignAquarius</t>
-        </is>
-      </c>
-      <c r="C194" t="n">
-        <v>2</v>
-      </c>
-      <c r="D194" t="n">
-        <v>75</v>
-      </c>
-      <c r="E194" t="n">
-        <v>3</v>
-      </c>
-      <c r="F194" t="n">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>SignAquarius</t>
-        </is>
-      </c>
-      <c r="C195" t="n">
-        <v>2</v>
-      </c>
-      <c r="D195" t="n">
-        <v>100</v>
-      </c>
-      <c r="E195" t="n">
-        <v>3</v>
-      </c>
-      <c r="F195" t="n">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>SignAquarius</t>
-        </is>
-      </c>
-      <c r="C196" t="n">
-        <v>3</v>
-      </c>
-      <c r="D196" t="n">
-        <v>0</v>
-      </c>
-      <c r="E196" t="n">
-        <v>3</v>
-      </c>
-      <c r="F196" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>SignAquarius</t>
-        </is>
-      </c>
-      <c r="C197" t="n">
-        <v>3</v>
-      </c>
-      <c r="D197" t="n">
-        <v>25</v>
-      </c>
-      <c r="E197" t="n">
-        <v>3</v>
-      </c>
-      <c r="F197" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>SignAquarius</t>
-        </is>
-      </c>
-      <c r="C198" t="n">
-        <v>3</v>
-      </c>
-      <c r="D198" t="n">
-        <v>50</v>
-      </c>
-      <c r="E198" t="n">
-        <v>3</v>
-      </c>
-      <c r="F198" t="n">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>SignAquarius</t>
-        </is>
-      </c>
-      <c r="C199" t="n">
-        <v>3</v>
-      </c>
-      <c r="D199" t="n">
-        <v>75</v>
-      </c>
-      <c r="E199" t="n">
-        <v>3</v>
-      </c>
-      <c r="F199" t="n">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>SignAquarius</t>
-        </is>
-      </c>
-      <c r="C200" t="n">
-        <v>3</v>
-      </c>
-      <c r="D200" t="n">
-        <v>100</v>
-      </c>
-      <c r="E200" t="n">
-        <v>3</v>
-      </c>
-      <c r="F200" t="n">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>SignPisces</t>
-        </is>
-      </c>
-      <c r="C201" t="n">
-        <v>1</v>
-      </c>
-      <c r="D201" t="n">
-        <v>0</v>
-      </c>
-      <c r="E201" t="n">
-        <v>3</v>
-      </c>
-      <c r="F201" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>SignPisces</t>
-        </is>
-      </c>
-      <c r="C202" t="n">
-        <v>1</v>
-      </c>
-      <c r="D202" t="n">
-        <v>25</v>
-      </c>
-      <c r="E202" t="n">
-        <v>3</v>
-      </c>
-      <c r="F202" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>SignPisces</t>
-        </is>
-      </c>
-      <c r="C203" t="n">
-        <v>1</v>
-      </c>
-      <c r="D203" t="n">
-        <v>50</v>
-      </c>
-      <c r="E203" t="n">
-        <v>3</v>
-      </c>
-      <c r="F203" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>SignPisces</t>
-        </is>
-      </c>
-      <c r="C204" t="n">
-        <v>1</v>
-      </c>
-      <c r="D204" t="n">
-        <v>75</v>
-      </c>
-      <c r="E204" t="n">
-        <v>3</v>
-      </c>
-      <c r="F204" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>SignPisces</t>
-        </is>
-      </c>
-      <c r="C205" t="n">
-        <v>1</v>
-      </c>
-      <c r="D205" t="n">
-        <v>100</v>
-      </c>
-      <c r="E205" t="n">
-        <v>3</v>
-      </c>
-      <c r="F205" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>SignPisces</t>
-        </is>
-      </c>
-      <c r="C206" t="n">
-        <v>2</v>
-      </c>
-      <c r="D206" t="n">
-        <v>0</v>
-      </c>
-      <c r="E206" t="n">
-        <v>3</v>
-      </c>
-      <c r="F206" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>SignPisces</t>
-        </is>
-      </c>
-      <c r="C207" t="n">
-        <v>2</v>
-      </c>
-      <c r="D207" t="n">
-        <v>25</v>
-      </c>
-      <c r="E207" t="n">
-        <v>3</v>
-      </c>
-      <c r="F207" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>SignPisces</t>
-        </is>
-      </c>
-      <c r="C208" t="n">
-        <v>2</v>
-      </c>
-      <c r="D208" t="n">
-        <v>50</v>
-      </c>
-      <c r="E208" t="n">
-        <v>3</v>
-      </c>
-      <c r="F208" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>SignPisces</t>
-        </is>
-      </c>
-      <c r="C209" t="n">
-        <v>2</v>
-      </c>
-      <c r="D209" t="n">
-        <v>75</v>
-      </c>
-      <c r="E209" t="n">
-        <v>3</v>
-      </c>
-      <c r="F209" t="n">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>SignPisces</t>
-        </is>
-      </c>
-      <c r="C210" t="n">
-        <v>2</v>
-      </c>
-      <c r="D210" t="n">
-        <v>100</v>
-      </c>
-      <c r="E210" t="n">
-        <v>3</v>
-      </c>
-      <c r="F210" t="n">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>SignPisces</t>
-        </is>
-      </c>
-      <c r="C211" t="n">
-        <v>3</v>
-      </c>
-      <c r="D211" t="n">
-        <v>0</v>
-      </c>
-      <c r="E211" t="n">
-        <v>3</v>
-      </c>
-      <c r="F211" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>SignPisces</t>
-        </is>
-      </c>
-      <c r="C212" t="n">
-        <v>3</v>
-      </c>
-      <c r="D212" t="n">
-        <v>25</v>
-      </c>
-      <c r="E212" t="n">
-        <v>3</v>
-      </c>
-      <c r="F212" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="213">
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>SignPisces</t>
-        </is>
-      </c>
-      <c r="C213" t="n">
-        <v>3</v>
-      </c>
-      <c r="D213" t="n">
-        <v>50</v>
-      </c>
-      <c r="E213" t="n">
-        <v>3</v>
-      </c>
-      <c r="F213" t="n">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="214">
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>SignPisces</t>
-        </is>
-      </c>
-      <c r="C214" t="n">
-        <v>3</v>
-      </c>
-      <c r="D214" t="n">
-        <v>75</v>
-      </c>
-      <c r="E214" t="n">
-        <v>3</v>
-      </c>
-      <c r="F214" t="n">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="215">
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>SignPisces</t>
-        </is>
-      </c>
-      <c r="C215" t="n">
-        <v>3</v>
-      </c>
-      <c r="D215" t="n">
-        <v>100</v>
-      </c>
-      <c r="E215" t="n">
-        <v>3</v>
-      </c>
-      <c r="F215" t="n">
-        <v>168</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/jingyuan_codex.xlsx
+++ b/Config/Datas/jingyuan_codex.xlsx
@@ -1602,7 +1602,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
@@ -1773,7 +1772,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="B6" t="n">
         <v>1</v>
@@ -2394,7 +2392,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
@@ -2603,7 +2600,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
@@ -2790,7 +2786,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>7,1</t>
+          <t>7,None,1</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2807,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>7,1</t>
+          <t>7,None,1</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2828,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>7,2</t>
+          <t>7,None,2</t>
         </is>
       </c>
     </row>
@@ -2853,7 +2849,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>7,1</t>
+          <t>7,None,1</t>
         </is>
       </c>
     </row>
@@ -2874,7 +2870,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>7,2</t>
+          <t>7,None,2</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2891,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>7,1</t>
+          <t>7,None,1</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2912,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>7,1</t>
+          <t>7,None,1</t>
         </is>
       </c>
     </row>
@@ -2937,7 +2933,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>7,1</t>
+          <t>7,None,1</t>
         </is>
       </c>
     </row>
@@ -2958,7 +2954,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>7,1</t>
+          <t>7,None,1</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2975,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>7,1</t>
+          <t>7,None,1</t>
         </is>
       </c>
     </row>
@@ -3000,7 +2996,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>7,1</t>
+          <t>7,None,1</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3017,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>7,1</t>
+          <t>7,None,1</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3038,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>7,1</t>
+          <t>7,None,1</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3059,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>7,1</t>
+          <t>7,None,1</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3080,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>7,1</t>
+          <t>7,None,1</t>
         </is>
       </c>
     </row>
@@ -4376,7 +4372,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
@@ -4899,7 +4894,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
@@ -5397,7 +5391,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>

--- a/Config/Datas/jingyuan_codex.xlsx
+++ b/Config/Datas/jingyuan_codex.xlsx
@@ -1602,54 +1602,55 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>npc_1_10</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+    </row>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>npc_1_10</t>
+          <t>npc_11_20</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>npc_11_20</t>
+          <t>npc_21_plus</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D7" t="n">
-        <v>20</v>
+        <v>999</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>npc_21_plus</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>21</v>
-      </c>
-      <c r="D8" t="n">
-        <v>999</v>
-      </c>
-      <c r="E8" t="n">
-        <v>3</v>
-      </c>
-    </row>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1772,9 +1773,27 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>orc</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>OrcI</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100</v>
+      </c>
+    </row>
     <row r="6">
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1783,7 +1802,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OrcI</t>
+          <t>OrcII</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1792,16 +1811,16 @@
     </row>
     <row r="7">
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>orc</t>
+          <t>human</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>OrcII</t>
+          <t>HumanI</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1810,7 +1829,7 @@
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1819,7 +1838,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>HumanI</t>
+          <t>HumanII</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1828,7 +1847,7 @@
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1837,7 +1856,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>HumanII</t>
+          <t>HumanIII</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1846,7 +1865,7 @@
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1855,7 +1874,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>HumanIII</t>
+          <t>HumanIV</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1864,7 +1883,7 @@
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1873,7 +1892,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HumanIV</t>
+          <t>HumanV</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1882,7 +1901,7 @@
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,7 +1910,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>HumanV</t>
+          <t>HumanVI</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1900,7 +1919,7 @@
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1909,7 +1928,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>HumanVI</t>
+          <t>HumanVII</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1918,7 +1937,7 @@
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1927,7 +1946,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>HumanVII</t>
+          <t>MonsterI</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1936,7 +1955,7 @@
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1945,7 +1964,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MonsterI</t>
+          <t>MonsterII</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1954,7 +1973,7 @@
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1963,31 +1982,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MonsterII</t>
+          <t>MonsterIII</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>100</v>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" t="n">
-        <v>12</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>human</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>MonsterIII</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>100</v>
-      </c>
-    </row>
+    <row r="17"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2392,52 +2394,53 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C5" t="n">
         <v>45</v>
       </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
         <v>35</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F5" t="n">
         <v>15</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G5" t="n">
         <v>10</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H5" t="n">
         <v>90</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I5" t="n">
         <v>4</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J5" t="n">
         <v>12</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K5" t="n">
         <v>12</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L5" t="n">
         <v>6</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M5" t="n">
         <v>35</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N5" t="n">
         <v>20</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O5" t="n">
         <v>20</v>
       </c>
     </row>
+    <row r="6"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2600,30 +2603,31 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>default</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>desire_crystal_01</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D5" t="n">
         <v>2</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E5" t="n">
         <v>80</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F5" t="n">
         <v>2</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G5" t="n">
         <v>2</v>
       </c>
     </row>
+    <row r="6"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4372,20 +4376,50 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>OrcI</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>兽人精元</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>jingyuan/orccommon</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>orc</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>orccommon</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+    </row>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>OrcI</t>
+          <t>OrcII</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>??I</t>
+          <t>兽人精英精元</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>jingyuan/orccommon</t>
+          <t>jingyuan/orcelite</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -4395,57 +4429,57 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>orci</t>
+          <t>orcelite</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>OrcII</t>
+          <t>HumanI</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>??II</t>
+          <t>白羊座精元</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>jingyuan/orcelite</t>
+          <t>jingyuan/signaries</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>orc</t>
+          <t>human</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>orcii</t>
+          <t>signaries</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>HumanI</t>
+          <t>HumanII</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>??I</t>
+          <t>金牛座精元</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>jingyuan/signaries</t>
+          <t>jingyuan/signtaurus</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -4455,27 +4489,27 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>humani</t>
+          <t>signtaurus</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>HumanII</t>
+          <t>HumanIII</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>??II</t>
+          <t>双子座精元</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>jingyuan/signtaurus</t>
+          <t>jingyuan/signgemini</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4485,27 +4519,27 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>humanii</t>
+          <t>signgemini</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>HumanIII</t>
+          <t>HumanIV</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>??III</t>
+          <t>巨蟹座精元</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>jingyuan/signgemini</t>
+          <t>jingyuan/signcancer</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4515,27 +4549,27 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>humaniii</t>
+          <t>signcancer</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>HumanIV</t>
+          <t>HumanV</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>??IV</t>
+          <t>狮子座精元</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>jingyuan/signcancer</t>
+          <t>jingyuan/signleo</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4545,27 +4579,27 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>humaniv</t>
+          <t>signleo</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>HumanV</t>
+          <t>HumanVI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>??V</t>
+          <t>处女座精元</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>jingyuan/signleo</t>
+          <t>jingyuan/signvirgo</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -4575,27 +4609,27 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>humanv</t>
+          <t>signvirgo</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>HumanVI</t>
+          <t>HumanVII</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>??VI</t>
+          <t>天秤座精元</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>jingyuan/signvirgo</t>
+          <t>jingyuan/signlibra</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -4605,27 +4639,27 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>humanvi</t>
+          <t>signlibra</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>HumanVII</t>
+          <t>MonsterI</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>??VII</t>
+          <t>天蝎座精元</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>jingyuan/signlibra</t>
+          <t>jingyuan/signscorpio</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -4635,103 +4669,74 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>humanvii</t>
+          <t>signscorpio</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>MonsterI</t>
+          <t>MonsterII</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>??I</t>
+          <t>射手座精元</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>jingyuan/signscorpio</t>
+          <t>jingyuan/signsagittarius</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>monster</t>
+          <t>human</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>monsteri</t>
+          <t>signsagittarius</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>MonsterII</t>
+          <t>MonsterIII</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>??II</t>
+          <t>摩羯座精元</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>jingyuan/signsagittarius</t>
+          <t>jingyuan/signcapricorn</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>monster</t>
+          <t>human</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>monsterii</t>
+          <t>signcapricorn</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>MonsterIII</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>??III</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>jingyuan/signcapricorn</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>monster</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>monsteriii</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
         <v>12</v>
       </c>
     </row>
+    <row r="17"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4894,20 +4899,50 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>premium_orccommon</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>OrcI</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>优质兽人精元</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>affix_orccommon</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>extract_or_event</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>premium_orci</t>
+          <t>premium_orcelite</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OrcI</t>
+          <t>OrcII</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>??优质兽人精元</t>
+          <t>优质兽人精英精元</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -4915,7 +4950,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>affix_orccommon</t>
+          <t>affix_orcelite</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -4927,17 +4962,17 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>premium_orcii</t>
+          <t>premium_signaries</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>OrcII</t>
+          <t>HumanI</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>??优质兽人精英精元</t>
+          <t>优质白羊座精元</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -4945,7 +4980,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>affix_orcelite</t>
+          <t>affix_signaries</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -4957,17 +4992,17 @@
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>premium_humani</t>
+          <t>premium_signtaurus</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HumanI</t>
+          <t>HumanII</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>??优质白羊座精元</t>
+          <t>优质金牛座精元</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -4975,7 +5010,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>affix_signaries</t>
+          <t>affix_signtaurus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -4987,17 +5022,17 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>premium_humanii</t>
+          <t>premium_signgemini</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HumanII</t>
+          <t>HumanIII</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>??优质金牛座精元</t>
+          <t>优质双子座精元</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -5005,7 +5040,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>affix_signtaurus</t>
+          <t>affix_signgemini</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -5017,17 +5052,17 @@
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>premium_humaniii</t>
+          <t>premium_signcancer</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>HumanIII</t>
+          <t>HumanIV</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>??优质双子座精元</t>
+          <t>优质巨蟹座精元</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -5035,7 +5070,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>affix_signgemini</t>
+          <t>affix_signcancer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -5047,17 +5082,17 @@
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>premium_humaniv</t>
+          <t>premium_signleo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HumanIV</t>
+          <t>HumanV</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>??优质巨蟹座精元</t>
+          <t>优质狮子座精元</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -5065,7 +5100,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>affix_signcancer</t>
+          <t>affix_signleo</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5077,17 +5112,17 @@
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>premium_humanv</t>
+          <t>premium_signvirgo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HumanV</t>
+          <t>HumanVI</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>??优质狮子座精元</t>
+          <t>优质处女座精元</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -5095,7 +5130,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>affix_signleo</t>
+          <t>affix_signvirgo</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5107,17 +5142,17 @@
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>premium_humanvi</t>
+          <t>premium_signlibra</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HumanVI</t>
+          <t>HumanVII</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>??优质处女座精元</t>
+          <t>优质天秤座精元</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -5125,7 +5160,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>affix_signvirgo</t>
+          <t>affix_signlibra</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5137,17 +5172,17 @@
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>premium_humanvii</t>
+          <t>premium_signscorpio</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>HumanVII</t>
+          <t>MonsterI</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>??优质天秤座精元</t>
+          <t>优质天蝎座精元</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -5155,7 +5190,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>affix_signlibra</t>
+          <t>affix_signscorpio</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -5167,17 +5202,17 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>premium_monsteri</t>
+          <t>premium_signsagittarius</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MonsterI</t>
+          <t>MonsterII</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>??优质天蝎座精元</t>
+          <t>优质射手座精元</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -5185,7 +5220,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>affix_signscorpio</t>
+          <t>affix_signsagittarius</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -5197,17 +5232,17 @@
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>premium_monsterii</t>
+          <t>premium_signcapricorn</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MonsterII</t>
+          <t>MonsterIII</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>??优质射手座精元</t>
+          <t>优质摩羯座精元</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -5215,7 +5250,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>affix_signsagittarius</t>
+          <t>affix_signcapricorn</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -5224,36 +5259,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>premium_monsteriii</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>MonsterIII</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>??优质摩羯座精元</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>3</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>affix_signcapricorn</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>extract_or_event</t>
-        </is>
-      </c>
-    </row>
+    <row r="17"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5391,6 +5397,25 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>OrcI</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
@@ -5401,13 +5426,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E6" t="n">
         <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -5420,13 +5445,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E7" t="n">
         <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -5439,13 +5464,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E8" t="n">
         <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -5458,13 +5483,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E9" t="n">
         <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -5474,16 +5499,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>3</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -5496,13 +5521,13 @@
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E11" t="n">
         <v>3</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -5515,13 +5540,13 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E12" t="n">
         <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13">
@@ -5534,13 +5559,13 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E13" t="n">
         <v>3</v>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -5553,13 +5578,13 @@
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E14" t="n">
         <v>3</v>
       </c>
       <c r="F14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -5569,16 +5594,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -5591,13 +5616,13 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E16" t="n">
         <v>3</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -5610,13 +5635,13 @@
         <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E17" t="n">
         <v>3</v>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -5629,13 +5654,13 @@
         <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E18" t="n">
         <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
@@ -5648,32 +5673,32 @@
         <v>3</v>
       </c>
       <c r="D19" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E19" t="n">
         <v>3</v>
       </c>
       <c r="F19" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>OrcI</t>
+          <t>OrcII</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>3</v>
       </c>
       <c r="F20" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -5686,13 +5711,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E21" t="n">
         <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -5705,13 +5730,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E22" t="n">
         <v>3</v>
       </c>
       <c r="F22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -5724,13 +5749,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E23" t="n">
         <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -5743,13 +5768,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E24" t="n">
         <v>3</v>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25">
@@ -5759,16 +5784,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -5781,13 +5806,13 @@
         <v>2</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E26" t="n">
         <v>3</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -5800,13 +5825,13 @@
         <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E27" t="n">
         <v>3</v>
       </c>
       <c r="F27" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
@@ -5819,13 +5844,13 @@
         <v>2</v>
       </c>
       <c r="D28" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E28" t="n">
         <v>3</v>
       </c>
       <c r="F28" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29">
@@ -5838,13 +5863,13 @@
         <v>2</v>
       </c>
       <c r="D29" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E29" t="n">
         <v>3</v>
       </c>
       <c r="F29" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
@@ -5854,16 +5879,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>3</v>
       </c>
       <c r="F30" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -5876,13 +5901,13 @@
         <v>3</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E31" t="n">
         <v>3</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32">
@@ -5895,13 +5920,13 @@
         <v>3</v>
       </c>
       <c r="D32" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E32" t="n">
         <v>3</v>
       </c>
       <c r="F32" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33">
@@ -5914,13 +5939,13 @@
         <v>3</v>
       </c>
       <c r="D33" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E33" t="n">
         <v>3</v>
       </c>
       <c r="F33" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34">
@@ -5933,32 +5958,32 @@
         <v>3</v>
       </c>
       <c r="D34" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E34" t="n">
         <v>3</v>
       </c>
       <c r="F34" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t>OrcII</t>
+          <t>HumanI</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>3</v>
       </c>
       <c r="F35" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -5971,13 +5996,13 @@
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E36" t="n">
         <v>3</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -5990,13 +6015,13 @@
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E37" t="n">
         <v>3</v>
       </c>
       <c r="F37" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
@@ -6009,13 +6034,13 @@
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E38" t="n">
         <v>3</v>
       </c>
       <c r="F38" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39">
@@ -6028,13 +6053,13 @@
         <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E39" t="n">
         <v>3</v>
       </c>
       <c r="F39" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40">
@@ -6044,16 +6069,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
         <v>3</v>
       </c>
       <c r="F40" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -6066,13 +6091,13 @@
         <v>2</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E41" t="n">
         <v>3</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
@@ -6085,13 +6110,13 @@
         <v>2</v>
       </c>
       <c r="D42" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E42" t="n">
         <v>3</v>
       </c>
       <c r="F42" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43">
@@ -6104,13 +6129,13 @@
         <v>2</v>
       </c>
       <c r="D43" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E43" t="n">
         <v>3</v>
       </c>
       <c r="F43" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44">
@@ -6123,13 +6148,13 @@
         <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E44" t="n">
         <v>3</v>
       </c>
       <c r="F44" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="45">
@@ -6139,16 +6164,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D45" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
         <v>3</v>
       </c>
       <c r="F45" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -6161,13 +6186,13 @@
         <v>3</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E46" t="n">
         <v>3</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47">
@@ -6180,13 +6205,13 @@
         <v>3</v>
       </c>
       <c r="D47" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E47" t="n">
         <v>3</v>
       </c>
       <c r="F47" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48">
@@ -6199,13 +6224,13 @@
         <v>3</v>
       </c>
       <c r="D48" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E48" t="n">
         <v>3</v>
       </c>
       <c r="F48" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="49">
@@ -6218,32 +6243,32 @@
         <v>3</v>
       </c>
       <c r="D49" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E49" t="n">
         <v>3</v>
       </c>
       <c r="F49" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="inlineStr">
         <is>
-          <t>HumanI</t>
+          <t>HumanII</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
         <v>3</v>
       </c>
       <c r="F50" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -6256,13 +6281,13 @@
         <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E51" t="n">
         <v>3</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
@@ -6275,13 +6300,13 @@
         <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E52" t="n">
         <v>3</v>
       </c>
       <c r="F52" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53">
@@ -6294,13 +6319,13 @@
         <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E53" t="n">
         <v>3</v>
       </c>
       <c r="F53" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="54">
@@ -6313,13 +6338,13 @@
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E54" t="n">
         <v>3</v>
       </c>
       <c r="F54" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="55">
@@ -6329,16 +6354,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
         <v>3</v>
       </c>
       <c r="F55" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -6351,13 +6376,13 @@
         <v>2</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E56" t="n">
         <v>3</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57">
@@ -6370,13 +6395,13 @@
         <v>2</v>
       </c>
       <c r="D57" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E57" t="n">
         <v>3</v>
       </c>
       <c r="F57" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="58">
@@ -6389,13 +6414,13 @@
         <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E58" t="n">
         <v>3</v>
       </c>
       <c r="F58" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="59">
@@ -6408,13 +6433,13 @@
         <v>2</v>
       </c>
       <c r="D59" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E59" t="n">
         <v>3</v>
       </c>
       <c r="F59" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="60">
@@ -6424,16 +6449,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D60" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
         <v>3</v>
       </c>
       <c r="F60" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -6446,13 +6471,13 @@
         <v>3</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E61" t="n">
         <v>3</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="62">
@@ -6465,13 +6490,13 @@
         <v>3</v>
       </c>
       <c r="D62" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E62" t="n">
         <v>3</v>
       </c>
       <c r="F62" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="63">
@@ -6484,13 +6509,13 @@
         <v>3</v>
       </c>
       <c r="D63" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E63" t="n">
         <v>3</v>
       </c>
       <c r="F63" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="64">
@@ -6503,32 +6528,32 @@
         <v>3</v>
       </c>
       <c r="D64" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E64" t="n">
         <v>3</v>
       </c>
       <c r="F64" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="65">
       <c r="B65" t="inlineStr">
         <is>
-          <t>HumanII</t>
+          <t>HumanIII</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E65" t="n">
         <v>3</v>
       </c>
       <c r="F65" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -6541,13 +6566,13 @@
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E66" t="n">
         <v>3</v>
       </c>
       <c r="F66" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
@@ -6560,13 +6585,13 @@
         <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E67" t="n">
         <v>3</v>
       </c>
       <c r="F67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68">
@@ -6579,13 +6604,13 @@
         <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E68" t="n">
         <v>3</v>
       </c>
       <c r="F68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69">
@@ -6598,13 +6623,13 @@
         <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E69" t="n">
         <v>3</v>
       </c>
       <c r="F69" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70">
@@ -6614,16 +6639,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D70" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E70" t="n">
         <v>3</v>
       </c>
       <c r="F70" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -6636,13 +6661,13 @@
         <v>2</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E71" t="n">
         <v>3</v>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72">
@@ -6655,13 +6680,13 @@
         <v>2</v>
       </c>
       <c r="D72" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E72" t="n">
         <v>3</v>
       </c>
       <c r="F72" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="73">
@@ -6674,13 +6699,13 @@
         <v>2</v>
       </c>
       <c r="D73" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E73" t="n">
         <v>3</v>
       </c>
       <c r="F73" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="74">
@@ -6693,13 +6718,13 @@
         <v>2</v>
       </c>
       <c r="D74" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E74" t="n">
         <v>3</v>
       </c>
       <c r="F74" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="75">
@@ -6709,16 +6734,16 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D75" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
         <v>3</v>
       </c>
       <c r="F75" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -6731,13 +6756,13 @@
         <v>3</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E76" t="n">
         <v>3</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="77">
@@ -6750,13 +6775,13 @@
         <v>3</v>
       </c>
       <c r="D77" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E77" t="n">
         <v>3</v>
       </c>
       <c r="F77" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="78">
@@ -6769,13 +6794,13 @@
         <v>3</v>
       </c>
       <c r="D78" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E78" t="n">
         <v>3</v>
       </c>
       <c r="F78" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
     </row>
     <row r="79">
@@ -6788,32 +6813,32 @@
         <v>3</v>
       </c>
       <c r="D79" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E79" t="n">
         <v>3</v>
       </c>
       <c r="F79" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
     </row>
     <row r="80">
       <c r="B80" t="inlineStr">
         <is>
-          <t>HumanIII</t>
+          <t>HumanIV</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
         <v>3</v>
       </c>
       <c r="F80" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -6826,13 +6851,13 @@
         <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E81" t="n">
         <v>3</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82">
@@ -6845,13 +6870,13 @@
         <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E82" t="n">
         <v>3</v>
       </c>
       <c r="F82" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="83">
@@ -6864,13 +6889,13 @@
         <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E83" t="n">
         <v>3</v>
       </c>
       <c r="F83" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="84">
@@ -6883,13 +6908,13 @@
         <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E84" t="n">
         <v>3</v>
       </c>
       <c r="F84" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="85">
@@ -6899,16 +6924,16 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D85" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
         <v>3</v>
       </c>
       <c r="F85" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -6921,13 +6946,13 @@
         <v>2</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E86" t="n">
         <v>3</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="87">
@@ -6940,13 +6965,13 @@
         <v>2</v>
       </c>
       <c r="D87" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E87" t="n">
         <v>3</v>
       </c>
       <c r="F87" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="88">
@@ -6959,13 +6984,13 @@
         <v>2</v>
       </c>
       <c r="D88" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E88" t="n">
         <v>3</v>
       </c>
       <c r="F88" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="89">
@@ -6978,13 +7003,13 @@
         <v>2</v>
       </c>
       <c r="D89" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E89" t="n">
         <v>3</v>
       </c>
       <c r="F89" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="90">
@@ -6994,16 +7019,16 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D90" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
         <v>3</v>
       </c>
       <c r="F90" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -7016,13 +7041,13 @@
         <v>3</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E91" t="n">
         <v>3</v>
       </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="92">
@@ -7035,13 +7060,13 @@
         <v>3</v>
       </c>
       <c r="D92" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E92" t="n">
         <v>3</v>
       </c>
       <c r="F92" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
     </row>
     <row r="93">
@@ -7054,13 +7079,13 @@
         <v>3</v>
       </c>
       <c r="D93" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E93" t="n">
         <v>3</v>
       </c>
       <c r="F93" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
     </row>
     <row r="94">
@@ -7073,32 +7098,32 @@
         <v>3</v>
       </c>
       <c r="D94" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E94" t="n">
         <v>3</v>
       </c>
       <c r="F94" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
     </row>
     <row r="95">
       <c r="B95" t="inlineStr">
         <is>
-          <t>HumanIV</t>
+          <t>HumanV</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
         <v>3</v>
       </c>
       <c r="F95" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -7111,13 +7136,13 @@
         <v>1</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E96" t="n">
         <v>3</v>
       </c>
       <c r="F96" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="97">
@@ -7130,13 +7155,13 @@
         <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E97" t="n">
         <v>3</v>
       </c>
       <c r="F97" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="98">
@@ -7149,13 +7174,13 @@
         <v>1</v>
       </c>
       <c r="D98" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E98" t="n">
         <v>3</v>
       </c>
       <c r="F98" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="99">
@@ -7168,13 +7193,13 @@
         <v>1</v>
       </c>
       <c r="D99" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E99" t="n">
         <v>3</v>
       </c>
       <c r="F99" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="100">
@@ -7184,16 +7209,16 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D100" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E100" t="n">
         <v>3</v>
       </c>
       <c r="F100" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -7206,13 +7231,13 @@
         <v>2</v>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E101" t="n">
         <v>3</v>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="102">
@@ -7225,13 +7250,13 @@
         <v>2</v>
       </c>
       <c r="D102" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E102" t="n">
         <v>3</v>
       </c>
       <c r="F102" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="103">
@@ -7244,13 +7269,13 @@
         <v>2</v>
       </c>
       <c r="D103" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E103" t="n">
         <v>3</v>
       </c>
       <c r="F103" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
     </row>
     <row r="104">
@@ -7263,13 +7288,13 @@
         <v>2</v>
       </c>
       <c r="D104" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E104" t="n">
         <v>3</v>
       </c>
       <c r="F104" t="n">
-        <v>42</v>
+        <v>56</v>
       </c>
     </row>
     <row r="105">
@@ -7279,16 +7304,16 @@
         </is>
       </c>
       <c r="C105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D105" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E105" t="n">
         <v>3</v>
       </c>
       <c r="F105" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -7301,13 +7326,13 @@
         <v>3</v>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E106" t="n">
         <v>3</v>
       </c>
       <c r="F106" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="107">
@@ -7320,13 +7345,13 @@
         <v>3</v>
       </c>
       <c r="D107" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E107" t="n">
         <v>3</v>
       </c>
       <c r="F107" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
     </row>
     <row r="108">
@@ -7339,13 +7364,13 @@
         <v>3</v>
       </c>
       <c r="D108" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E108" t="n">
         <v>3</v>
       </c>
       <c r="F108" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
     </row>
     <row r="109">
@@ -7358,32 +7383,32 @@
         <v>3</v>
       </c>
       <c r="D109" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E109" t="n">
         <v>3</v>
       </c>
       <c r="F109" t="n">
-        <v>63</v>
+        <v>84</v>
       </c>
     </row>
     <row r="110">
       <c r="B110" t="inlineStr">
         <is>
-          <t>HumanV</t>
+          <t>HumanVI</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D110" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E110" t="n">
         <v>3</v>
       </c>
       <c r="F110" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -7396,13 +7421,13 @@
         <v>1</v>
       </c>
       <c r="D111" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E111" t="n">
         <v>3</v>
       </c>
       <c r="F111" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="112">
@@ -7415,13 +7440,13 @@
         <v>1</v>
       </c>
       <c r="D112" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E112" t="n">
         <v>3</v>
       </c>
       <c r="F112" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="113">
@@ -7434,13 +7459,13 @@
         <v>1</v>
       </c>
       <c r="D113" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E113" t="n">
         <v>3</v>
       </c>
       <c r="F113" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="114">
@@ -7453,13 +7478,13 @@
         <v>1</v>
       </c>
       <c r="D114" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E114" t="n">
         <v>3</v>
       </c>
       <c r="F114" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="115">
@@ -7469,16 +7494,16 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D115" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E115" t="n">
         <v>3</v>
       </c>
       <c r="F115" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -7491,13 +7516,13 @@
         <v>2</v>
       </c>
       <c r="D116" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E116" t="n">
         <v>3</v>
       </c>
       <c r="F116" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="117">
@@ -7510,13 +7535,13 @@
         <v>2</v>
       </c>
       <c r="D117" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E117" t="n">
         <v>3</v>
       </c>
       <c r="F117" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
     </row>
     <row r="118">
@@ -7529,13 +7554,13 @@
         <v>2</v>
       </c>
       <c r="D118" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E118" t="n">
         <v>3</v>
       </c>
       <c r="F118" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
     </row>
     <row r="119">
@@ -7548,13 +7573,13 @@
         <v>2</v>
       </c>
       <c r="D119" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E119" t="n">
         <v>3</v>
       </c>
       <c r="F119" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
     </row>
     <row r="120">
@@ -7564,16 +7589,16 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D120" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E120" t="n">
         <v>3</v>
       </c>
       <c r="F120" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -7586,13 +7611,13 @@
         <v>3</v>
       </c>
       <c r="D121" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E121" t="n">
         <v>3</v>
       </c>
       <c r="F121" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="122">
@@ -7605,13 +7630,13 @@
         <v>3</v>
       </c>
       <c r="D122" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E122" t="n">
         <v>3</v>
       </c>
       <c r="F122" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
     </row>
     <row r="123">
@@ -7624,13 +7649,13 @@
         <v>3</v>
       </c>
       <c r="D123" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E123" t="n">
         <v>3</v>
       </c>
       <c r="F123" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
     </row>
     <row r="124">
@@ -7643,32 +7668,32 @@
         <v>3</v>
       </c>
       <c r="D124" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E124" t="n">
         <v>3</v>
       </c>
       <c r="F124" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
     </row>
     <row r="125">
       <c r="B125" t="inlineStr">
         <is>
-          <t>HumanVI</t>
+          <t>HumanVII</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D125" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E125" t="n">
         <v>3</v>
       </c>
       <c r="F125" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -7681,13 +7706,13 @@
         <v>1</v>
       </c>
       <c r="D126" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E126" t="n">
         <v>3</v>
       </c>
       <c r="F126" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="127">
@@ -7700,13 +7725,13 @@
         <v>1</v>
       </c>
       <c r="D127" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E127" t="n">
         <v>3</v>
       </c>
       <c r="F127" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="128">
@@ -7719,13 +7744,13 @@
         <v>1</v>
       </c>
       <c r="D128" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E128" t="n">
         <v>3</v>
       </c>
       <c r="F128" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="129">
@@ -7738,13 +7763,13 @@
         <v>1</v>
       </c>
       <c r="D129" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E129" t="n">
         <v>3</v>
       </c>
       <c r="F129" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
     </row>
     <row r="130">
@@ -7754,16 +7779,16 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D130" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E130" t="n">
         <v>3</v>
       </c>
       <c r="F130" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -7776,13 +7801,13 @@
         <v>2</v>
       </c>
       <c r="D131" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E131" t="n">
         <v>3</v>
       </c>
       <c r="F131" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="132">
@@ -7795,13 +7820,13 @@
         <v>2</v>
       </c>
       <c r="D132" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E132" t="n">
         <v>3</v>
       </c>
       <c r="F132" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
     </row>
     <row r="133">
@@ -7814,13 +7839,13 @@
         <v>2</v>
       </c>
       <c r="D133" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E133" t="n">
         <v>3</v>
       </c>
       <c r="F133" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
     </row>
     <row r="134">
@@ -7833,13 +7858,13 @@
         <v>2</v>
       </c>
       <c r="D134" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E134" t="n">
         <v>3</v>
       </c>
       <c r="F134" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
     </row>
     <row r="135">
@@ -7849,16 +7874,16 @@
         </is>
       </c>
       <c r="C135" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D135" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E135" t="n">
         <v>3</v>
       </c>
       <c r="F135" t="n">
-        <v>72</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
@@ -7871,13 +7896,13 @@
         <v>3</v>
       </c>
       <c r="D136" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E136" t="n">
         <v>3</v>
       </c>
       <c r="F136" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="137">
@@ -7890,13 +7915,13 @@
         <v>3</v>
       </c>
       <c r="D137" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E137" t="n">
         <v>3</v>
       </c>
       <c r="F137" t="n">
-        <v>27</v>
+        <v>54</v>
       </c>
     </row>
     <row r="138">
@@ -7909,13 +7934,13 @@
         <v>3</v>
       </c>
       <c r="D138" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E138" t="n">
         <v>3</v>
       </c>
       <c r="F138" t="n">
-        <v>54</v>
+        <v>81</v>
       </c>
     </row>
     <row r="139">
@@ -7928,32 +7953,32 @@
         <v>3</v>
       </c>
       <c r="D139" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E139" t="n">
         <v>3</v>
       </c>
       <c r="F139" t="n">
-        <v>81</v>
+        <v>108</v>
       </c>
     </row>
     <row r="140">
       <c r="B140" t="inlineStr">
         <is>
-          <t>HumanVII</t>
+          <t>MonsterI</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D140" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E140" t="n">
         <v>3</v>
       </c>
       <c r="F140" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -7966,13 +7991,13 @@
         <v>1</v>
       </c>
       <c r="D141" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E141" t="n">
         <v>3</v>
       </c>
       <c r="F141" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="142">
@@ -7985,13 +8010,13 @@
         <v>1</v>
       </c>
       <c r="D142" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E142" t="n">
         <v>3</v>
       </c>
       <c r="F142" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="143">
@@ -8004,13 +8029,13 @@
         <v>1</v>
       </c>
       <c r="D143" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E143" t="n">
         <v>3</v>
       </c>
       <c r="F143" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="144">
@@ -8023,13 +8048,13 @@
         <v>1</v>
       </c>
       <c r="D144" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E144" t="n">
         <v>3</v>
       </c>
       <c r="F144" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="145">
@@ -8039,16 +8064,16 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D145" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E145" t="n">
         <v>3</v>
       </c>
       <c r="F145" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -8061,13 +8086,13 @@
         <v>2</v>
       </c>
       <c r="D146" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E146" t="n">
         <v>3</v>
       </c>
       <c r="F146" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="147">
@@ -8080,13 +8105,13 @@
         <v>2</v>
       </c>
       <c r="D147" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E147" t="n">
         <v>3</v>
       </c>
       <c r="F147" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="148">
@@ -8099,13 +8124,13 @@
         <v>2</v>
       </c>
       <c r="D148" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E148" t="n">
         <v>3</v>
       </c>
       <c r="F148" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="149">
@@ -8118,13 +8143,13 @@
         <v>2</v>
       </c>
       <c r="D149" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E149" t="n">
         <v>3</v>
       </c>
       <c r="F149" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="150">
@@ -8134,16 +8159,16 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D150" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E150" t="n">
         <v>3</v>
       </c>
       <c r="F150" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -8156,13 +8181,13 @@
         <v>3</v>
       </c>
       <c r="D151" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E151" t="n">
         <v>3</v>
       </c>
       <c r="F151" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="152">
@@ -8175,13 +8200,13 @@
         <v>3</v>
       </c>
       <c r="D152" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E152" t="n">
         <v>3</v>
       </c>
       <c r="F152" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="153">
@@ -8194,13 +8219,13 @@
         <v>3</v>
       </c>
       <c r="D153" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E153" t="n">
         <v>3</v>
       </c>
       <c r="F153" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
     </row>
     <row r="154">
@@ -8213,32 +8238,32 @@
         <v>3</v>
       </c>
       <c r="D154" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E154" t="n">
         <v>3</v>
       </c>
       <c r="F154" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="155">
       <c r="B155" t="inlineStr">
         <is>
-          <t>MonsterI</t>
+          <t>MonsterII</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D155" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E155" t="n">
         <v>3</v>
       </c>
       <c r="F155" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -8251,13 +8276,13 @@
         <v>1</v>
       </c>
       <c r="D156" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E156" t="n">
         <v>3</v>
       </c>
       <c r="F156" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="157">
@@ -8270,13 +8295,13 @@
         <v>1</v>
       </c>
       <c r="D157" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E157" t="n">
         <v>3</v>
       </c>
       <c r="F157" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="158">
@@ -8289,13 +8314,13 @@
         <v>1</v>
       </c>
       <c r="D158" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E158" t="n">
         <v>3</v>
       </c>
       <c r="F158" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="159">
@@ -8308,13 +8333,13 @@
         <v>1</v>
       </c>
       <c r="D159" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E159" t="n">
         <v>3</v>
       </c>
       <c r="F159" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
     </row>
     <row r="160">
@@ -8324,16 +8349,16 @@
         </is>
       </c>
       <c r="C160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D160" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E160" t="n">
         <v>3</v>
       </c>
       <c r="F160" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -8346,13 +8371,13 @@
         <v>2</v>
       </c>
       <c r="D161" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E161" t="n">
         <v>3</v>
       </c>
       <c r="F161" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="162">
@@ -8365,13 +8390,13 @@
         <v>2</v>
       </c>
       <c r="D162" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E162" t="n">
         <v>3</v>
       </c>
       <c r="F162" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
     </row>
     <row r="163">
@@ -8384,13 +8409,13 @@
         <v>2</v>
       </c>
       <c r="D163" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E163" t="n">
         <v>3</v>
       </c>
       <c r="F163" t="n">
-        <v>44</v>
+        <v>66</v>
       </c>
     </row>
     <row r="164">
@@ -8403,13 +8428,13 @@
         <v>2</v>
       </c>
       <c r="D164" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E164" t="n">
         <v>3</v>
       </c>
       <c r="F164" t="n">
-        <v>66</v>
+        <v>88</v>
       </c>
     </row>
     <row r="165">
@@ -8419,16 +8444,16 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D165" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E165" t="n">
         <v>3</v>
       </c>
       <c r="F165" t="n">
-        <v>88</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166">
@@ -8441,13 +8466,13 @@
         <v>3</v>
       </c>
       <c r="D166" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E166" t="n">
         <v>3</v>
       </c>
       <c r="F166" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
     </row>
     <row r="167">
@@ -8460,13 +8485,13 @@
         <v>3</v>
       </c>
       <c r="D167" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E167" t="n">
         <v>3</v>
       </c>
       <c r="F167" t="n">
-        <v>33</v>
+        <v>66</v>
       </c>
     </row>
     <row r="168">
@@ -8479,13 +8504,13 @@
         <v>3</v>
       </c>
       <c r="D168" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E168" t="n">
         <v>3</v>
       </c>
       <c r="F168" t="n">
-        <v>66</v>
+        <v>99</v>
       </c>
     </row>
     <row r="169">
@@ -8498,32 +8523,32 @@
         <v>3</v>
       </c>
       <c r="D169" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E169" t="n">
         <v>3</v>
       </c>
       <c r="F169" t="n">
-        <v>99</v>
+        <v>132</v>
       </c>
     </row>
     <row r="170">
       <c r="B170" t="inlineStr">
         <is>
-          <t>MonsterII</t>
+          <t>MonsterIII</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D170" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E170" t="n">
         <v>3</v>
       </c>
       <c r="F170" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -8536,13 +8561,13 @@
         <v>1</v>
       </c>
       <c r="D171" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E171" t="n">
         <v>3</v>
       </c>
       <c r="F171" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="172">
@@ -8555,13 +8580,13 @@
         <v>1</v>
       </c>
       <c r="D172" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E172" t="n">
         <v>3</v>
       </c>
       <c r="F172" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="173">
@@ -8574,13 +8599,13 @@
         <v>1</v>
       </c>
       <c r="D173" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E173" t="n">
         <v>3</v>
       </c>
       <c r="F173" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
     </row>
     <row r="174">
@@ -8593,13 +8618,13 @@
         <v>1</v>
       </c>
       <c r="D174" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E174" t="n">
         <v>3</v>
       </c>
       <c r="F174" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="175">
@@ -8609,16 +8634,16 @@
         </is>
       </c>
       <c r="C175" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D175" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E175" t="n">
         <v>3</v>
       </c>
       <c r="F175" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
@@ -8631,13 +8656,13 @@
         <v>2</v>
       </c>
       <c r="D176" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E176" t="n">
         <v>3</v>
       </c>
       <c r="F176" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="177">
@@ -8650,13 +8675,13 @@
         <v>2</v>
       </c>
       <c r="D177" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E177" t="n">
         <v>3</v>
       </c>
       <c r="F177" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
     </row>
     <row r="178">
@@ -8669,13 +8694,13 @@
         <v>2</v>
       </c>
       <c r="D178" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E178" t="n">
         <v>3</v>
       </c>
       <c r="F178" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
     </row>
     <row r="179">
@@ -8688,13 +8713,13 @@
         <v>2</v>
       </c>
       <c r="D179" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E179" t="n">
         <v>3</v>
       </c>
       <c r="F179" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
     </row>
     <row r="180">
@@ -8704,16 +8729,16 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D180" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E180" t="n">
         <v>3</v>
       </c>
       <c r="F180" t="n">
-        <v>96</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181">
@@ -8726,13 +8751,13 @@
         <v>3</v>
       </c>
       <c r="D181" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E181" t="n">
         <v>3</v>
       </c>
       <c r="F181" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="182">
@@ -8745,13 +8770,13 @@
         <v>3</v>
       </c>
       <c r="D182" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E182" t="n">
         <v>3</v>
       </c>
       <c r="F182" t="n">
-        <v>36</v>
+        <v>72</v>
       </c>
     </row>
     <row r="183">
@@ -8764,13 +8789,13 @@
         <v>3</v>
       </c>
       <c r="D183" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="E183" t="n">
         <v>3</v>
       </c>
       <c r="F183" t="n">
-        <v>72</v>
+        <v>108</v>
       </c>
     </row>
     <row r="184">
@@ -8783,34 +8808,16 @@
         <v>3</v>
       </c>
       <c r="D184" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E184" t="n">
         <v>3</v>
       </c>
       <c r="F184" t="n">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>MonsterIII</t>
-        </is>
-      </c>
-      <c r="C185" t="n">
-        <v>3</v>
-      </c>
-      <c r="D185" t="n">
-        <v>100</v>
-      </c>
-      <c r="E185" t="n">
-        <v>3</v>
-      </c>
-      <c r="F185" t="n">
         <v>144</v>
       </c>
     </row>
+    <row r="185"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
